--- a/Files/Ha entregar/COCOMO II - ADAPTADO - 2026.xlsx
+++ b/Files/Ha entregar/COCOMO II - ADAPTADO - 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimde\Desktop\2026 unu\ing de sf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/323874764bc4b245/Desktop/RutasMTC/Files/Ha entregar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F432FD-DC84-4564-9984-0BD484B6E6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{09F432FD-DC84-4564-9984-0BD484B6E6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4F102F8-8A34-4457-B15C-98A8B31BA202}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="702" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elementos Funcionales" sheetId="19" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="_Toc308084624" localSheetId="0">'Elementos Funcionales'!#REF!</definedName>
     <definedName name="OLE_LINK1" localSheetId="3">'Costo Desarrollo'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,6 +35,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -124,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="313">
   <si>
     <t>Total</t>
   </si>
@@ -332,45 +334,6 @@
   </si>
   <si>
     <t>Complejidad: 1= Baja, 3=Media, 6=Alta 8+Muy alta</t>
-  </si>
-  <si>
-    <t>CU-CDC-002 CONFIGURACIÓN PUNTAJES POR VARIABLE</t>
-  </si>
-  <si>
-    <t>CU-CDC-003 CREAR MODELOS DE CALIFICACIÓN POR MODALIDAD DE CRÉDITO</t>
-  </si>
-  <si>
-    <t>CU-CDC-004  ASOCIAR VARIABLES AL MODELO DE CALIFICACIÓN</t>
-  </si>
-  <si>
-    <t>CU-CDC-005 DEFINICIÓN REQUISITOS BÁSICOS DE ADJUDICACIÓN</t>
-  </si>
-  <si>
-    <t>CU-CDC-006 VERIFICAR REQUISITOS BÁSICOS DE ADJUDICACIÓN</t>
-  </si>
-  <si>
-    <t>CU-CDC-009 ESTIMAR VALOR A FINANCIAR POR CRÉDITO, SUBSIDIO Y ALIANZA POR SOLICITUD DE CRÉDITO</t>
-  </si>
-  <si>
-    <t>CU-CDC-015 PUBLICAR RESULTADOS DE COMITÉ DE CRÉDITO</t>
-  </si>
-  <si>
-    <t>CU-CDC-017 APROBACIÓN DE CRÉDITOS POR EXCEPCIÓN</t>
-  </si>
-  <si>
-    <t>CU-CDC-018 ACTUALIZACIÓN DESCARGA ARCHIVO DE COMITÉ</t>
-  </si>
-  <si>
-    <t>CU-CDC-022 CONFIGURAR VARIABLE DE PUNTAJE MÍNIMO</t>
-  </si>
-  <si>
-    <t>CU-CDC-023 GENERAR LOG DE AUDITORÍA DEL PROCESO DE COMITÉ DE CRÉDITO</t>
-  </si>
-  <si>
-    <t>CU-CDC-025 CARGAR INFORMACIÓN DE BECARIOS</t>
-  </si>
-  <si>
-    <t>CU-CDC-026 CONFIGURAR CALENDARIOS DE COMITÉ DE CRÉDITO</t>
   </si>
   <si>
     <t>Costo Hora desarrollo</t>
@@ -949,9 +912,6 @@
     <t>Multiplicador (fijo)</t>
   </si>
   <si>
-    <t>Proyecto 'PRUEBA 1'</t>
-  </si>
-  <si>
     <t>T_Costo mes (miles)</t>
   </si>
   <si>
@@ -1345,48 +1305,6 @@
     <t>Consultas + formato + exportación + generacion de documento</t>
   </si>
   <si>
-    <t>CU-ZAP-001  REGISTRAR EMPLEADO (RF01)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-002  MODIFICAR DATOS DEL EMPLEADO (RF02)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-003  DAR DE BAJA / ELIMINAR EMPLEADO (RF03)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-004  CONSULTAR EMPLEADOS (RF04)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-005  GESTIONAR ÁREAS (RF05)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-006  CALCULAR EDAD DEL EMPLEADO (RF06)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-007  CALCULAR ANTIGÜEDAD LABORAL (RF07)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-008  CALCULAR GRATIFICACIONES Y DESCUENTOS DE PLANILLA (RF08)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-009  GENERAR BOLETA DE PAGO (RF09)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-010  EXPORTAR INFORMACIÓN A EXCEL (RF10)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-011  VALIDAR DNI DEL EMPLEADO (RF11)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-012  AUTENTICAR USUARIO Y CONTROLAR ROLES (RF12)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-013  GENERAR REPORTES POR ÁREA (RF13)</t>
-  </si>
-  <si>
-    <t>CU-ZAP-014  BÚSQUEDA RÁPIDA DE EMPLEADOS (RF14)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Insumo (T_Costo mes): </t>
     </r>
@@ -1396,7 +1314,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Tiene un valor de mercado de S/. 4,145.56 por un mes completo.</t>
+      <t>Tiene un valor de mercado de S/. 4,140.78 por un mes completo.</t>
     </r>
   </si>
   <si>
@@ -1422,7 +1340,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Se termina pagando S/. 829.11, lo que demuestra que su costo se distribuye equitativamente de forma puntual a lo largo de todo el ciclo de vida del software para labores de supervisión y control.</t>
+      <t xml:space="preserve"> Se termina pagando S/. 828.16, lo que demuestra que su costo se distribuye equitativamente de forma puntual a lo largo de todo el ciclo de vida del software para labores de supervisión y control.</t>
     </r>
   </si>
   <si>
@@ -1435,7 +1353,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Su tarifa base es de S/. 5,181.95 mensuales.</t>
+      <t xml:space="preserve"> Su tarifa base es de S/. 5,175.98 mensuales.</t>
     </r>
   </si>
   <si>
@@ -1461,7 +1379,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Su costo final es de S/. 1,295.49, evidenciando que es un recurso clave al principio para definir las reglas del sistema y al final para validar la aceptación del producto</t>
+      <t>Su costo final es de S/. 1,293.99, evidenciando que es un recurso clave al principio para definir las reglas del sistema y al final para validar la aceptación del producto</t>
     </r>
     <r>
       <rPr>
@@ -1483,7 +1401,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Posee una valoración mensual de S/. 6,218.34.</t>
+      <t xml:space="preserve"> Posee una valoración mensual de S/. 6,211.17.</t>
     </r>
   </si>
   <si>
@@ -1509,7 +1427,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>El proyecto devenga S/. 1,865.50 por su labor, resaltando que la definición técnica inicial y la configuración de los servidores en producción son vitales.</t>
+      <t>El proyecto devenga S/. 1,863.35 por su labor, resaltando que la definición técnica inicial y la configuración de los servidores en producción son vitales.</t>
     </r>
   </si>
   <si>
@@ -1522,7 +1440,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Es el perfil con mayor sueldo base, ascendiendo a S/. 11,400.30 por mes.</t>
+      <t>Es el perfil con mayor sueldo base, ascendiendo a S/. 11,387.15 por mes.</t>
     </r>
   </si>
   <si>
@@ -1548,7 +1466,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Representa el gasto más fuerte del proyecto con S/. 6,270.16, reafirmando que la fase de codificación pura es el núcleo del proyecto y la etapa que consume mayor esfuerzo.</t>
+      <t>Representa el gasto más fuerte del proyecto con S/. 6,262.93, reafirmando que la fase de codificación pura es el núcleo del proyecto y la etapa que consume mayor esfuerzo.</t>
     </r>
   </si>
   <si>
@@ -1561,7 +1479,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Su base mensual está valorizada en S/. 7,254.73.</t>
+      <t xml:space="preserve"> Su base mensual está valorizada en S/. 7,246.37.</t>
     </r>
   </si>
   <si>
@@ -1587,11 +1505,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Genera un costo parcial de S/. 2,539.16, demostrando una asignación estratégica para realizar pruebas tempranas y una validación exhaustiva (QA) antes del lanzamiento en vivo.</t>
-    </r>
-  </si>
-  <si>
-    <t>Se debe cobrar el Costo Parcial Total (S/. 12,799.42) más un margen de utilidad y gastos operativos, tomando como referencia de validación los S/. 20,727.81 que estimó el modelo COCOMO II. Si el precio final con ganancia se acerca a la cifra de COCOMO II, la propuesta económica es técnicamente sólida y competitiva.</t>
+      <t xml:space="preserve"> Genera un costo parcial de S/. 2,536.23, demostrando una asignación estratégica para realizar pruebas tempranas y una validación exhaustiva (QA) antes del lanzamiento en vivo.</t>
+    </r>
+  </si>
+  <si>
+    <t>Se debe cobrar el Costo Parcial Total (S/. 12,784.66) más un margen de utilidad y gastos operativos, tomando como referencia de validación los S/. 20,703.90 que estimó el modelo COCOMO II. Si el precio final con ganancia se acerca a la cifra de COCOMO II, la propuesta económica es técnicamente sólida y competitiva.</t>
   </si>
   <si>
     <t>Proyecto 'RUTAS MTC' · RT-2026-001 — Sistema Web de Rutas Turísticas Peatonales desde Estaciones Ferroviarias</t>
@@ -1668,17 +1586,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="11">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;S/.&quot;\ #,##0.00;&quot;S/.&quot;\ \-#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="_([$$-240A]\ * #,##0.00_);_([$$-240A]\ * \(#,##0.00\);_([$$-240A]\ * &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-240A]\ * #,##0.00_ ;_-[$$-240A]\ * \-#,##0.00\ ;_-[$$-240A]\ * &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="171" formatCode="_ [$S/.-280A]\ * #,##0.00_ ;_ [$S/.-280A]\ * \-#,##0.00_ ;_ [$S/.-280A]\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="[$S/.-280A]\ #,##0.00;[$S/.-280A]\ \-#,##0.00"/>
-    <numFmt numFmtId="173" formatCode="&quot;S/.&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="&quot;S/.&quot;\ #,##0.00;&quot;S/.&quot;\ \-#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="_([$$-240A]\ * #,##0.00_);_([$$-240A]\ * \(#,##0.00\);_([$$-240A]\ * &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="_-[$$-240A]\ * #,##0.00_ ;_-[$$-240A]\ * \-#,##0.00\ ;_-[$$-240A]\ * &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="172" formatCode="_ [$S/.-280A]\ * #,##0.00_ ;_ [$S/.-280A]\ * \-#,##0.00_ ;_ [$S/.-280A]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="[$S/.-280A]\ #,##0.00;[$S/.-280A]\ \-#,##0.00"/>
+    <numFmt numFmtId="174" formatCode="&quot;S/.&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="45" x14ac:knownFonts="1">
     <font>
@@ -1956,7 +1874,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2076,32 +1994,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -2320,19 +2214,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2341,10 +2222,10 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2417,7 +2298,7 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2470,9 +2351,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2489,7 +2367,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2526,8 +2404,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2540,14 +2418,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2562,7 +2440,7 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2572,13 +2450,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2746,17 +2624,113 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2771,9 +2745,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2800,110 +2771,11 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2928,45 +2800,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3134,6 +2967,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3424,193 +3261,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="6" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" style="6" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="2.44140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="49.44140625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="6" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="2.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49.42578125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="6" customWidth="1"/>
     <col min="10" max="10" width="9" style="6" customWidth="1"/>
     <col min="11" max="11" width="10" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="11.44140625" style="6"/>
+    <col min="12" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="D1" s="174" t="s">
-        <v>157</v>
-      </c>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-    </row>
-    <row r="2" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="C2" s="106" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="171" t="s">
-        <v>318</v>
-      </c>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="173"/>
-    </row>
-    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="D4" s="58" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="61"/>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+      <c r="D1" s="166" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+    </row>
+    <row r="2" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+      <c r="C2" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="163" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="165"/>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="D4" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="58"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="60"/>
       <c r="I4" s="44"/>
     </row>
-    <row r="5" spans="1:11" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="165" t="s">
+    <row r="5" spans="1:11" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="156" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="166"/>
+      <c r="B5" s="157"/>
       <c r="D5" s="11" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="H5" s="35" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="44"/>
     </row>
-    <row r="6" spans="1:11" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>1</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="49">
         <v>1</v>
       </c>
-      <c r="E6" s="109" t="s">
+      <c r="E6" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="49">
         <v>1</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="49">
         <f>COUNTIF($E$15:$E$36,"=Simple")</f>
-      </c>
-      <c r="H6" s="107" t="s">
-        <v>172</v>
+        <v>3</v>
+      </c>
+      <c r="H6" s="106" t="s">
+        <v>158</v>
       </c>
       <c r="I6" s="44"/>
     </row>
-    <row r="7" spans="1:11" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>2</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="50">
+      <c r="D7" s="49">
         <v>2</v>
       </c>
-      <c r="E7" s="109" t="s">
+      <c r="E7" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="49">
         <v>3</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="49">
         <f>COUNTIF($E$15:$E$36,"=Promedio")</f>
-      </c>
-      <c r="H7" s="107" t="s">
-        <v>173</v>
+        <v>9</v>
+      </c>
+      <c r="H7" s="106" t="s">
+        <v>159</v>
       </c>
       <c r="I7" s="44"/>
     </row>
-    <row r="8" spans="1:11" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>3</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="49">
         <v>3</v>
       </c>
-      <c r="E8" s="109" t="s">
+      <c r="E8" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="50">
+      <c r="F8" s="49">
         <v>6</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="49">
         <f>COUNTIF($E$15:$E$36,"=Complejo")</f>
-      </c>
-      <c r="H8" s="107" t="s">
-        <v>174</v>
+        <v>10</v>
+      </c>
+      <c r="H8" s="106" t="s">
+        <v>160</v>
       </c>
       <c r="I8" s="44"/>
     </row>
-    <row r="9" spans="1:11" ht="30.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>4</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="50">
+      <c r="D9" s="49">
         <v>4</v>
       </c>
-      <c r="E9" s="109" t="s">
+      <c r="E9" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="49">
         <v>8</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="49">
         <f>COUNTIF($E$15:$E$36,"=Muy Complejo")</f>
-      </c>
-      <c r="H9" s="107" t="s">
-        <v>175</v>
+        <v>0</v>
+      </c>
+      <c r="H9" s="106" t="s">
+        <v>161</v>
       </c>
       <c r="I9" s="44"/>
     </row>
-    <row r="10" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="165" t="s">
+    <row r="10" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="166"/>
-      <c r="D10" s="155" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="155"/>
+      <c r="B10" s="157"/>
+      <c r="D10" s="160" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="160"/>
       <c r="F10" s="34">
         <f>F6*G6+F7*G7+F8*G8+F9*G9</f>
+        <v>90</v>
       </c>
       <c r="G10" s="35">
         <f>SUM(G6:G9)</f>
+        <v>22</v>
       </c>
       <c r="I10" s="44"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="19"/>
       <c r="B11" s="43"/>
       <c r="D11" s="19"/>
@@ -3620,7 +3463,7 @@
       <c r="H11" s="33"/>
       <c r="I11" s="44"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="19"/>
       <c r="B12" s="43"/>
       <c r="D12" s="19"/>
@@ -3630,32 +3473,32 @@
       <c r="H12" s="33"/>
       <c r="I12" s="44"/>
     </row>
-    <row r="13" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="52"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="35" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="G13" s="169" t="s">
-        <v>178</v>
-      </c>
-      <c r="H13" s="169"/>
+        <v>146</v>
+      </c>
+      <c r="G13" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" s="161"/>
       <c r="I13" s="45" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="35" t="s">
         <v>44</v>
       </c>
@@ -3669,420 +3512,442 @@
         <v>45</v>
       </c>
       <c r="F14" s="34"/>
-      <c r="G14" s="170" t="s">
-        <v>148</v>
-      </c>
-      <c r="H14" s="170"/>
+      <c r="G14" s="162" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="162"/>
       <c r="I14" s="46"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="56"/>
-    </row>
-    <row r="15" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+    </row>
+    <row r="15" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D15" s="13">
         <v>1</v>
       </c>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F15" s="13">
-        <f>SUMIF(E$6:E$9,E15,F$6:F$9)</f>
-      </c>
-      <c r="G15" s="167" t="s">
-        <v>319</v>
-      </c>
-      <c r="H15" s="168"/>
+        <f t="shared" ref="F15:F36" si="0">SUMIF(E$6:E$9,E15,F$6:F$9)</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="158" t="s">
+        <v>291</v>
+      </c>
+      <c r="H15" s="159"/>
       <c r="I15" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="K15" s="55"/>
-    </row>
-    <row r="16" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="K15" s="54"/>
+    </row>
+    <row r="16" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="13">
         <v>2</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="13">
-        <f>SUMIF(E$6:E$9,E16,F$6:F$9)</f>
-      </c>
-      <c r="G16" s="167" t="s">
-        <v>320</v>
-      </c>
-      <c r="H16" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G16" s="158" t="s">
+        <v>292</v>
+      </c>
+      <c r="H16" s="159"/>
       <c r="I16" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="53"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="52"/>
       <c r="D17" s="13">
         <v>3</v>
       </c>
-      <c r="E17" s="63" t="s">
+      <c r="E17" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F17" s="13">
-        <f>SUMIF(E$6:E$9,E17,F$6:F$9)</f>
-      </c>
-      <c r="G17" s="167" t="s">
-        <v>321</v>
-      </c>
-      <c r="H17" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G17" s="158" t="s">
+        <v>293</v>
+      </c>
+      <c r="H17" s="159"/>
       <c r="I17" s="13" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="J17" s="19"/>
     </row>
-    <row r="18" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D18" s="13">
         <v>4</v>
       </c>
-      <c r="E18" s="63" t="s">
+      <c r="E18" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F18" s="13">
-        <f>SUMIF(E$6:E$9,E18,F$6:F$9)</f>
-      </c>
-      <c r="G18" s="167" t="s">
-        <v>322</v>
-      </c>
-      <c r="H18" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G18" s="158" t="s">
+        <v>294</v>
+      </c>
+      <c r="H18" s="159"/>
       <c r="I18" s="13" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="J18" s="19"/>
     </row>
-    <row r="19" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D19" s="13">
         <v>5</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F19" s="13">
-        <f>SUMIF(E$6:E$9,E19,F$6:F$9)</f>
-      </c>
-      <c r="G19" s="167" t="s">
-        <v>323</v>
-      </c>
-      <c r="H19" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G19" s="158" t="s">
+        <v>295</v>
+      </c>
+      <c r="H19" s="159"/>
       <c r="I19" s="13" t="s">
         <v>63</v>
       </c>
       <c r="J19" s="19"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="53"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.2">
+      <c r="C20" s="52"/>
       <c r="D20" s="13">
         <v>6</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="13">
-        <f>SUMIF(E$6:E$9,E20,F$6:F$9)</f>
-      </c>
-      <c r="G20" s="167" t="s">
-        <v>324</v>
-      </c>
-      <c r="H20" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G20" s="158" t="s">
+        <v>296</v>
+      </c>
+      <c r="H20" s="159"/>
       <c r="I20" s="13" t="s">
         <v>63</v>
       </c>
       <c r="J20" s="19"/>
     </row>
-    <row r="21" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D21" s="13">
         <v>7</v>
       </c>
-      <c r="E21" s="63" t="s">
+      <c r="E21" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F21" s="13">
-        <f>SUMIF(E$6:E$9,E21,F$6:F$9)</f>
-      </c>
-      <c r="G21" s="167" t="s">
-        <v>325</v>
-      </c>
-      <c r="H21" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G21" s="158" t="s">
+        <v>297</v>
+      </c>
+      <c r="H21" s="159"/>
       <c r="I21" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.2">
       <c r="D22" s="13">
         <v>8</v>
       </c>
-      <c r="E22" s="63" t="s">
+      <c r="E22" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="13">
-        <f>SUMIF(E$6:E$9,E22,F$6:F$9)</f>
-      </c>
-      <c r="G22" s="167" t="s">
-        <v>326</v>
-      </c>
-      <c r="H22" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G22" s="158" t="s">
+        <v>298</v>
+      </c>
+      <c r="H22" s="159"/>
       <c r="I22" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.2">
       <c r="D23" s="13">
         <v>9</v>
       </c>
-      <c r="E23" s="63" t="s">
+      <c r="E23" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F23" s="13">
-        <f>SUMIF(E$6:E$9,E23,F$6:F$9)</f>
-      </c>
-      <c r="G23" s="167" t="s">
-        <v>327</v>
-      </c>
-      <c r="H23" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G23" s="158" t="s">
+        <v>299</v>
+      </c>
+      <c r="H23" s="159"/>
       <c r="I23" s="13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.2">
       <c r="D24" s="13">
         <v>10</v>
       </c>
-      <c r="E24" s="63" t="s">
+      <c r="E24" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F24" s="13">
-        <f>SUMIF(E$6:E$9,E24,F$6:F$9)</f>
-      </c>
-      <c r="G24" s="167" t="s">
-        <v>328</v>
-      </c>
-      <c r="H24" s="168"/>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G24" s="158" t="s">
+        <v>300</v>
+      </c>
+      <c r="H24" s="159"/>
       <c r="I24" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.2">
       <c r="D25" s="13">
         <v>11</v>
       </c>
-      <c r="E25" s="63" t="s">
+      <c r="E25" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F25" s="13">
-        <f>SUMIF(E$6:E$9,E25,F$6:F$9)</f>
-      </c>
-      <c r="G25" s="167" t="s">
-        <v>329</v>
-      </c>
-      <c r="H25" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G25" s="158" t="s">
+        <v>301</v>
+      </c>
+      <c r="H25" s="159"/>
       <c r="I25" s="13" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D26" s="13">
         <v>12</v>
       </c>
-      <c r="E26" s="63" t="s">
+      <c r="E26" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F26" s="13">
-        <f>SUMIF(E$6:E$9,E26,F$6:F$9)</f>
-      </c>
-      <c r="G26" s="167" t="s">
-        <v>330</v>
-      </c>
-      <c r="H26" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G26" s="158" t="s">
+        <v>302</v>
+      </c>
+      <c r="H26" s="159"/>
       <c r="I26" s="13" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.2">
       <c r="D27" s="13">
         <v>13</v>
       </c>
-      <c r="E27" s="63" t="s">
+      <c r="E27" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F27" s="13">
-        <f>SUMIF(E$6:E$9,E27,F$6:F$9)</f>
-      </c>
-      <c r="G27" s="167" t="s">
-        <v>331</v>
-      </c>
-      <c r="H27" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G27" s="158" t="s">
+        <v>303</v>
+      </c>
+      <c r="H27" s="159"/>
       <c r="I27" s="13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.2">
       <c r="D28" s="13">
         <v>14</v>
       </c>
-      <c r="E28" s="63" t="s">
+      <c r="E28" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F28" s="13">
-        <f>SUMIF(E$6:E$9,E28,F$6:F$9)</f>
-      </c>
-      <c r="G28" s="167" t="s">
-        <v>332</v>
-      </c>
-      <c r="H28" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G28" s="158" t="s">
+        <v>304</v>
+      </c>
+      <c r="H28" s="159"/>
       <c r="I28" s="13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D29" s="13">
         <v>15</v>
       </c>
-      <c r="E29" s="63" t="s">
+      <c r="E29" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F29" s="13">
-        <f>SUMIF(E$6:E$9,E29,F$6:F$9)</f>
-      </c>
-      <c r="G29" s="167" t="s">
-        <v>333</v>
-      </c>
-      <c r="H29" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G29" s="158" t="s">
+        <v>305</v>
+      </c>
+      <c r="H29" s="159"/>
       <c r="I29" s="13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D30" s="13">
         <v>16</v>
       </c>
-      <c r="E30" s="63" t="s">
+      <c r="E30" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F30" s="13">
-        <f>SUMIF(E$6:E$9,E30,F$6:F$9)</f>
-      </c>
-      <c r="G30" s="167" t="s">
-        <v>334</v>
-      </c>
-      <c r="H30" s="168"/>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G30" s="158" t="s">
+        <v>306</v>
+      </c>
+      <c r="H30" s="159"/>
       <c r="I30" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D31" s="13">
         <v>17</v>
       </c>
-      <c r="E31" s="63" t="s">
+      <c r="E31" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F31" s="13">
-        <f>SUMIF(E$6:E$9,E31,F$6:F$9)</f>
-      </c>
-      <c r="G31" s="167" t="s">
-        <v>335</v>
-      </c>
-      <c r="H31" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G31" s="158" t="s">
+        <v>307</v>
+      </c>
+      <c r="H31" s="159"/>
       <c r="I31" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="J31" s="55"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J31" s="54"/>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.2">
       <c r="D32" s="13">
         <v>18</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F32" s="13">
-        <f>SUMIF(E$6:E$9,E32,F$6:F$9)</f>
-      </c>
-      <c r="G32" s="167" t="s">
-        <v>336</v>
-      </c>
-      <c r="H32" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G32" s="158" t="s">
+        <v>308</v>
+      </c>
+      <c r="H32" s="159"/>
       <c r="I32" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="J32" s="53"/>
-    </row>
-    <row r="33" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J32" s="52"/>
+    </row>
+    <row r="33" spans="4:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D33" s="13">
         <v>19</v>
       </c>
-      <c r="E33" s="63" t="s">
+      <c r="E33" s="62" t="s">
         <v>31</v>
       </c>
       <c r="F33" s="13">
-        <f>SUMIF(E$6:E$9,E33,F$6:F$9)</f>
-      </c>
-      <c r="G33" s="167" t="s">
-        <v>337</v>
-      </c>
-      <c r="H33" s="168"/>
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G33" s="158" t="s">
+        <v>309</v>
+      </c>
+      <c r="H33" s="159"/>
       <c r="I33" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="J33" s="57"/>
-    </row>
-    <row r="34" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J33" s="56"/>
+    </row>
+    <row r="34" spans="4:10" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D34" s="13">
         <v>20</v>
       </c>
-      <c r="E34" s="63" t="s">
+      <c r="E34" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F34" s="13">
-        <f>SUMIF(E$6:E$9,E34,F$6:F$9)</f>
-      </c>
-      <c r="G34" s="167" t="s">
-        <v>338</v>
-      </c>
-      <c r="H34" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G34" s="158" t="s">
+        <v>310</v>
+      </c>
+      <c r="H34" s="159"/>
       <c r="I34" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="J34" s="53"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="J34" s="52"/>
+    </row>
+    <row r="35" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D35" s="13">
         <v>21</v>
       </c>
-      <c r="E35" s="63" t="s">
+      <c r="E35" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F35" s="13">
-        <f>SUMIF(E$6:E$9,E35,F$6:F$9)</f>
-      </c>
-      <c r="G35" s="167" t="s">
-        <v>339</v>
-      </c>
-      <c r="H35" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G35" s="158" t="s">
+        <v>311</v>
+      </c>
+      <c r="H35" s="159"/>
       <c r="I35" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="J35" s="57"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="J35" s="56"/>
+    </row>
+    <row r="36" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D36" s="13">
         <v>22</v>
       </c>
-      <c r="E36" s="63" t="s">
+      <c r="E36" s="62" t="s">
         <v>30</v>
       </c>
       <c r="F36" s="13">
-        <f>SUMIF(E$6:E$9,E36,F$6:F$9)</f>
-      </c>
-      <c r="G36" s="167" t="s">
-        <v>340</v>
-      </c>
-      <c r="H36" s="168"/>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G36" s="158" t="s">
+        <v>312</v>
+      </c>
+      <c r="H36" s="159"/>
       <c r="I36" s="13" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4131,472 +3996,487 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AA26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" style="7" customWidth="1"/>
     <col min="2" max="2" width="3" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="7" customWidth="1"/>
     <col min="6" max="6" width="51" style="9" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="7"/>
+    <col min="7" max="7" width="9.140625" style="7"/>
     <col min="8" max="8" width="5" style="7" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" style="7"/>
-    <col min="11" max="11" width="11.21875" style="7" customWidth="1"/>
-    <col min="12" max="12" width="18.5546875" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="7"/>
+    <col min="9" max="9" width="12.7109375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="7"/>
+    <col min="11" max="11" width="11.28515625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="18.5703125" style="7" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I1" s="180" t="s">
-        <v>149</v>
-      </c>
-      <c r="J1" s="180"/>
-      <c r="K1" s="180"/>
-      <c r="L1" s="180"/>
+      <c r="I1" s="151" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
       <c r="M1" s="10"/>
     </row>
-    <row r="2" spans="2:27" s="10" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183" t="s">
+    <row r="2" spans="2:27" s="10" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="96" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" s="96" t="s">
+      <c r="C2" s="154"/>
+      <c r="D2" s="95" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="95" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:27" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="97">
+    <row r="3" spans="2:27" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="96">
         <v>1</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="C3" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="92">
+      <c r="D3" s="91">
         <v>2</v>
       </c>
-      <c r="E3" s="93">
+      <c r="E3" s="92">
         <v>4</v>
       </c>
-      <c r="F3" s="95" t="s">
+      <c r="F3" s="94" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="10">
         <f>D3*E3</f>
-      </c>
-      <c r="I3" s="100" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="101" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="2:27" s="10" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.25">
-      <c r="B4" s="97">
+      <c r="J3" s="100" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.2">
+      <c r="B4" s="96">
         <v>2</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="92">
+      <c r="D4" s="91">
         <v>1</v>
       </c>
-      <c r="E4" s="93">
+      <c r="E4" s="92">
         <v>4</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="94" t="s">
         <v>47</v>
       </c>
       <c r="G4" s="10">
         <f t="shared" ref="G4:G15" si="0">D4*E4</f>
-      </c>
-      <c r="I4" s="102">
+        <v>4</v>
+      </c>
+      <c r="I4" s="101">
         <v>0</v>
       </c>
-      <c r="J4" s="103" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="2:27" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="B5" s="97">
+      <c r="J4" s="102" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+      <c r="B5" s="96">
         <v>3</v>
       </c>
-      <c r="C5" s="94" t="s">
+      <c r="C5" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="92">
+      <c r="D5" s="91">
         <v>1</v>
       </c>
-      <c r="E5" s="93">
+      <c r="E5" s="92">
         <v>4</v>
       </c>
-      <c r="F5" s="95" t="s">
+      <c r="F5" s="94" t="s">
         <v>48</v>
       </c>
       <c r="G5" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="I5" s="102">
+        <v>4</v>
+      </c>
+      <c r="I5" s="101">
         <v>1</v>
       </c>
-      <c r="J5" s="103" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y5" s="175" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z5" s="175"/>
-      <c r="AA5" s="175"/>
-    </row>
-    <row r="6" spans="2:27" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="B6" s="97">
+      <c r="J5" s="102" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y5" s="146" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z5" s="146"/>
+      <c r="AA5" s="146"/>
+    </row>
+    <row r="6" spans="2:27" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.2">
+      <c r="B6" s="96">
         <v>4</v>
       </c>
-      <c r="C6" s="94" t="s">
+      <c r="C6" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="91">
         <v>1</v>
       </c>
-      <c r="E6" s="93">
+      <c r="E6" s="92">
         <v>5</v>
       </c>
-      <c r="F6" s="95" t="s">
+      <c r="F6" s="94" t="s">
         <v>49</v>
       </c>
       <c r="G6" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="I6" s="102">
+        <v>5</v>
+      </c>
+      <c r="I6" s="101">
         <v>2</v>
       </c>
-      <c r="J6" s="103" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y6" s="175"/>
-      <c r="Z6" s="175"/>
-      <c r="AA6" s="175"/>
-    </row>
-    <row r="7" spans="2:27" s="10" customFormat="1" ht="57" x14ac:dyDescent="0.25">
-      <c r="B7" s="97">
+      <c r="J6" s="102" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y6" s="146"/>
+      <c r="Z6" s="146"/>
+      <c r="AA6" s="146"/>
+    </row>
+    <row r="7" spans="2:27" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.2">
+      <c r="B7" s="96">
         <v>5</v>
       </c>
-      <c r="C7" s="94" t="s">
+      <c r="C7" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="91">
         <v>1</v>
       </c>
-      <c r="E7" s="93">
+      <c r="E7" s="92">
         <v>4</v>
       </c>
-      <c r="F7" s="95" t="s">
+      <c r="F7" s="94" t="s">
         <v>50</v>
       </c>
       <c r="G7" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="I7" s="102">
+        <v>4</v>
+      </c>
+      <c r="I7" s="101">
         <v>3</v>
       </c>
-      <c r="J7" s="103" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="2:27" s="10" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.25">
-      <c r="B8" s="97">
+      <c r="J7" s="102" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="2:27" s="10" customFormat="1" ht="36" x14ac:dyDescent="0.2">
+      <c r="B8" s="96">
         <v>6</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="92">
+      <c r="D8" s="91">
         <v>0.5</v>
       </c>
-      <c r="E8" s="93">
+      <c r="E8" s="92">
         <v>2</v>
       </c>
-      <c r="F8" s="95" t="s">
+      <c r="F8" s="94" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="I8" s="102">
+        <v>1</v>
+      </c>
+      <c r="I8" s="101">
         <v>4</v>
       </c>
-      <c r="J8" s="103" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" spans="2:27" s="10" customFormat="1" ht="34.799999999999997" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="97">
+      <c r="J8" s="102" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="2:27" s="10" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="96">
         <v>7</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="91">
         <v>0.5</v>
       </c>
-      <c r="E9" s="93">
+      <c r="E9" s="92">
         <v>5</v>
       </c>
-      <c r="F9" s="95" t="s">
+      <c r="F9" s="94" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="I9" s="104">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="103">
         <v>5</v>
       </c>
-      <c r="J9" s="105" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="2:27" s="10" customFormat="1" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="B10" s="97">
+      <c r="J9" s="104" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="2:27" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+      <c r="B10" s="96">
         <v>8</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="91">
         <v>2</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="92">
         <v>3</v>
       </c>
-      <c r="F10" s="95" t="s">
+      <c r="F10" s="94" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="10">
         <f t="shared" si="0"/>
-      </c>
-    </row>
-    <row r="11" spans="2:27" s="10" customFormat="1" ht="34.799999999999997" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:27" s="10" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="96">
         <v>9</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="92">
+      <c r="D11" s="91">
         <v>1</v>
       </c>
-      <c r="E11" s="93">
+      <c r="E11" s="92">
         <v>4</v>
       </c>
-      <c r="F11" s="95" t="s">
+      <c r="F11" s="94" t="s">
         <v>52</v>
       </c>
       <c r="G11" s="10">
         <f t="shared" si="0"/>
-      </c>
-    </row>
-    <row r="12" spans="2:27" s="10" customFormat="1" ht="45.6" x14ac:dyDescent="0.25">
-      <c r="B12" s="97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" s="10" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="B12" s="96">
         <v>10</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="91">
         <v>1</v>
       </c>
-      <c r="E12" s="93">
+      <c r="E12" s="92">
         <v>2</v>
       </c>
-      <c r="F12" s="95" t="s">
+      <c r="F12" s="94" t="s">
         <v>53</v>
       </c>
       <c r="G12" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="K12" s="140" t="s">
-        <v>274</v>
-      </c>
-      <c r="L12" s="141" t="s">
-        <v>275</v>
-      </c>
-      <c r="M12" s="176" t="s">
-        <v>276</v>
-      </c>
-      <c r="N12" s="176"/>
-      <c r="O12" s="176"/>
-      <c r="P12" s="176"/>
-      <c r="Q12" s="177"/>
-    </row>
-    <row r="13" spans="2:27" s="10" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="97">
+        <v>2</v>
+      </c>
+      <c r="K12" s="139" t="s">
+        <v>260</v>
+      </c>
+      <c r="L12" s="140" t="s">
+        <v>261</v>
+      </c>
+      <c r="M12" s="147" t="s">
+        <v>262</v>
+      </c>
+      <c r="N12" s="147"/>
+      <c r="O12" s="147"/>
+      <c r="P12" s="147"/>
+      <c r="Q12" s="148"/>
+    </row>
+    <row r="13" spans="2:27" s="10" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="96">
         <v>11</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="92">
+      <c r="D13" s="91">
         <v>1</v>
       </c>
-      <c r="E13" s="93">
+      <c r="E13" s="92">
         <v>4</v>
       </c>
-      <c r="F13" s="95" t="s">
-        <v>273</v>
+      <c r="F13" s="94" t="s">
+        <v>259</v>
       </c>
       <c r="G13" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="K13" s="143">
+        <v>4</v>
+      </c>
+      <c r="K13" s="142">
         <v>0</v>
       </c>
-      <c r="L13" s="139" t="s">
-        <v>152</v>
-      </c>
-      <c r="M13" s="178" t="s">
-        <v>277</v>
-      </c>
-      <c r="N13" s="178"/>
-      <c r="O13" s="178"/>
-      <c r="P13" s="178"/>
-      <c r="Q13" s="179"/>
-    </row>
-    <row r="14" spans="2:27" s="10" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="97">
+      <c r="L13" s="138" t="s">
+        <v>139</v>
+      </c>
+      <c r="M13" s="149" t="s">
+        <v>263</v>
+      </c>
+      <c r="N13" s="149"/>
+      <c r="O13" s="149"/>
+      <c r="P13" s="149"/>
+      <c r="Q13" s="150"/>
+    </row>
+    <row r="14" spans="2:27" s="10" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="96">
         <v>12</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="92">
+      <c r="D14" s="91">
         <v>1</v>
       </c>
-      <c r="E14" s="93">
+      <c r="E14" s="92">
         <v>4</v>
       </c>
-      <c r="F14" s="95" t="s">
+      <c r="F14" s="94" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="K14" s="143">
+        <v>4</v>
+      </c>
+      <c r="K14" s="142">
         <v>1</v>
       </c>
-      <c r="L14" s="139" t="s">
-        <v>153</v>
-      </c>
-      <c r="M14" s="178" t="s">
-        <v>278</v>
-      </c>
-      <c r="N14" s="178"/>
-      <c r="O14" s="178"/>
-      <c r="P14" s="178"/>
-      <c r="Q14" s="179"/>
-    </row>
-    <row r="15" spans="2:27" s="10" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="97">
+      <c r="L14" s="138" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="149" t="s">
+        <v>264</v>
+      </c>
+      <c r="N14" s="149"/>
+      <c r="O14" s="149"/>
+      <c r="P14" s="149"/>
+      <c r="Q14" s="150"/>
+    </row>
+    <row r="15" spans="2:27" s="10" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="96">
         <v>13</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="92">
+      <c r="D15" s="91">
         <v>1</v>
       </c>
-      <c r="E15" s="93">
-        <v>1</v>
-      </c>
-      <c r="F15" s="95" t="s">
+      <c r="E15" s="92">
+        <v>2</v>
+      </c>
+      <c r="F15" s="94" t="s">
         <v>55</v>
       </c>
       <c r="G15" s="10">
         <f t="shared" si="0"/>
-      </c>
-      <c r="K15" s="143">
         <v>2</v>
       </c>
-      <c r="L15" s="139" t="s">
-        <v>151</v>
-      </c>
-      <c r="M15" s="178" t="s">
-        <v>279</v>
-      </c>
-      <c r="N15" s="178"/>
-      <c r="O15" s="178"/>
-      <c r="P15" s="178"/>
-      <c r="Q15" s="179"/>
+      <c r="K15" s="142">
+        <v>2</v>
+      </c>
+      <c r="L15" s="138" t="s">
+        <v>138</v>
+      </c>
+      <c r="M15" s="149" t="s">
+        <v>265</v>
+      </c>
+      <c r="N15" s="149"/>
+      <c r="O15" s="149"/>
+      <c r="P15" s="149"/>
+      <c r="Q15" s="150"/>
     </row>
     <row r="16" spans="2:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="184" t="s">
+      <c r="B16" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="184"/>
-      <c r="D16" s="98"/>
+      <c r="C16" s="155"/>
+      <c r="D16" s="97"/>
       <c r="E16" s="46">
         <f t="array" ref="E16">0.6+(SUM(D3:D15*E3:E15)/100)</f>
-      </c>
-      <c r="F16" s="99"/>
+        <v>1.105</v>
+      </c>
+      <c r="F16" s="98"/>
       <c r="G16" s="7">
         <f>0.6+SUM(G3:G15)/100</f>
-      </c>
-      <c r="K16" s="143">
+        <v>1.105</v>
+      </c>
+      <c r="K16" s="142">
         <v>3</v>
       </c>
-      <c r="L16" s="139" t="s">
-        <v>156</v>
-      </c>
-      <c r="M16" s="178" t="s">
-        <v>280</v>
-      </c>
-      <c r="N16" s="178"/>
-      <c r="O16" s="178"/>
-      <c r="P16" s="178"/>
-      <c r="Q16" s="179"/>
-    </row>
-    <row r="17" spans="11:17" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K17" s="143">
+      <c r="L16" s="138" t="s">
+        <v>143</v>
+      </c>
+      <c r="M16" s="149" t="s">
+        <v>266</v>
+      </c>
+      <c r="N16" s="149"/>
+      <c r="O16" s="149"/>
+      <c r="P16" s="149"/>
+      <c r="Q16" s="150"/>
+    </row>
+    <row r="17" spans="11:17" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K17" s="142">
         <v>4</v>
       </c>
-      <c r="L17" s="139" t="s">
-        <v>155</v>
-      </c>
-      <c r="M17" s="178" t="s">
-        <v>281</v>
-      </c>
-      <c r="N17" s="178"/>
-      <c r="O17" s="178"/>
-      <c r="P17" s="178"/>
-      <c r="Q17" s="179"/>
-    </row>
-    <row r="18" spans="11:17" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="K18" s="144">
+      <c r="L17" s="138" t="s">
+        <v>142</v>
+      </c>
+      <c r="M17" s="149" t="s">
+        <v>267</v>
+      </c>
+      <c r="N17" s="149"/>
+      <c r="O17" s="149"/>
+      <c r="P17" s="149"/>
+      <c r="Q17" s="150"/>
+    </row>
+    <row r="18" spans="11:17" ht="34.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="K18" s="143">
         <v>5</v>
       </c>
-      <c r="L18" s="142" t="s">
-        <v>154</v>
-      </c>
-      <c r="M18" s="181" t="s">
-        <v>282</v>
-      </c>
-      <c r="N18" s="181"/>
-      <c r="O18" s="181"/>
-      <c r="P18" s="181"/>
-      <c r="Q18" s="182"/>
+      <c r="L18" s="141" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="152" t="s">
+        <v>268</v>
+      </c>
+      <c r="N18" s="152"/>
+      <c r="O18" s="152"/>
+      <c r="P18" s="152"/>
+      <c r="Q18" s="153"/>
     </row>
     <row r="21" spans="11:17" ht="66" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="11:17" ht="66" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="11:17" ht="66" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="11:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="11:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="11:17" ht="79.2" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="11:17" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="11:17" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="11:17" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="I1:L1"/>
@@ -4620,392 +4500,409 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
-    <col min="4" max="4" width="36.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="84" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="192" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="193"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="194">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="83" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="176" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="177"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="90" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="167">
         <f>E34</f>
-      </c>
-      <c r="C2" s="195"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="91" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="194">
+        <v>9900</v>
+      </c>
+      <c r="C2" s="168"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="90" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="167">
         <f>B2/1000</f>
-      </c>
-      <c r="C3" s="195"/>
-    </row>
-    <row r="5" spans="1:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="196" t="s">
+        <v>9.9</v>
+      </c>
+      <c r="C3" s="168"/>
+    </row>
+    <row r="5" spans="1:8" ht="22.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="178" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="178"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="111" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="180" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="181"/>
+      <c r="D6" s="111" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="107" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="127">
+        <v>200</v>
+      </c>
+      <c r="C7" s="127">
+        <v>400</v>
+      </c>
+      <c r="D7" s="107" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="107" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="127">
+        <v>150</v>
+      </c>
+      <c r="C8" s="127">
+        <v>350</v>
+      </c>
+      <c r="D8" s="107" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="107" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="127">
+        <v>400</v>
+      </c>
+      <c r="C9" s="127">
+        <v>800</v>
+      </c>
+      <c r="D9" s="107" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="127">
+        <v>300</v>
+      </c>
+      <c r="C10" s="127">
+        <v>600</v>
+      </c>
+      <c r="D10" s="107" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="107" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" s="127">
+        <v>500</v>
+      </c>
+      <c r="C11" s="127">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="107" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="107" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="127">
+        <v>500</v>
+      </c>
+      <c r="C12" s="127">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="107" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="144"/>
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="144"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="144"/>
+      <c r="B14" s="145"/>
+      <c r="C14" s="145"/>
+      <c r="D14" s="144"/>
+    </row>
+    <row r="17" spans="1:14" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A17" s="179" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="179"/>
+      <c r="C17" s="179"/>
+      <c r="D17" s="179"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="180" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="181"/>
+      <c r="D18" s="109" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="110" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="110" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="110" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="107" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="110" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" s="110" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="110" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="107" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="110" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="110" t="s">
+        <v>228</v>
+      </c>
+      <c r="C21" s="110" t="s">
+        <v>229</v>
+      </c>
+      <c r="D21" s="107" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="112" t="s">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="110" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="198" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="199"/>
-      <c r="D6" s="112" t="s">
+      <c r="B22" s="110" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="110" t="s">
+        <v>230</v>
+      </c>
+      <c r="D22" s="107" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="110" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="108" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="128">
-        <v>200</v>
-      </c>
-      <c r="C7" s="128">
-        <v>400</v>
-      </c>
-      <c r="D7" s="108" t="s">
+      <c r="B23" s="110" t="s">
+        <v>230</v>
+      </c>
+      <c r="C23" s="110" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" s="107" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="108" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="128">
-        <v>150</v>
-      </c>
-      <c r="C8" s="128">
-        <v>350</v>
-      </c>
-      <c r="D8" s="108" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="108" t="s">
+    <row r="25" spans="1:14" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A25" s="179"/>
+      <c r="B25" s="179"/>
+      <c r="C25" s="179"/>
+      <c r="D25" s="179"/>
+    </row>
+    <row r="26" spans="1:14" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="170" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="171"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="172"/>
+      <c r="J26" s="169" t="s">
+        <v>232</v>
+      </c>
+      <c r="K26" s="169"/>
+      <c r="L26" s="169"/>
+      <c r="M26" s="169"/>
+      <c r="N26" s="169"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="131" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="173" t="s">
+        <v>224</v>
+      </c>
+      <c r="C27" s="174"/>
+      <c r="D27" s="132" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" s="132" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="129" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="167">
+        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Registro")</f>
+        <v>5</v>
+      </c>
+      <c r="C28" s="168"/>
+      <c r="D28" s="130">
+        <f>(B7+C7)/2</f>
+        <v>300</v>
+      </c>
+      <c r="E28" s="65">
+        <f t="shared" ref="E28:E33" si="0">B28*D28</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="128">
-        <v>400</v>
-      </c>
-      <c r="C9" s="128">
-        <v>800</v>
-      </c>
-      <c r="D9" s="108" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="108" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="128">
-        <v>300</v>
-      </c>
-      <c r="C10" s="128">
+      <c r="B29" s="167">
+        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Proceso")</f>
+        <v>5</v>
+      </c>
+      <c r="C29" s="168"/>
+      <c r="D29" s="130">
+        <f>(B9+C9)/2</f>
         <v>600</v>
       </c>
-      <c r="D10" s="108" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="108" t="s">
-        <v>285</v>
-      </c>
-      <c r="B11" s="128">
-        <v>500</v>
-      </c>
-      <c r="C11" s="128">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="108" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="108" t="s">
-        <v>181</v>
-      </c>
-      <c r="B12" s="128">
-        <v>500</v>
-      </c>
-      <c r="C12" s="128">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="108" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="145"/>
-      <c r="B13" s="146"/>
-      <c r="C13" s="146"/>
-      <c r="D13" s="145"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="145"/>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="145"/>
-    </row>
-    <row r="17" spans="1:14" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A17" s="197" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" s="197"/>
-      <c r="C17" s="197"/>
-      <c r="D17" s="197"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="110" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="198" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" s="199"/>
-      <c r="D18" s="110" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="111" t="s">
-        <v>226</v>
-      </c>
-      <c r="B19" s="111" t="s">
-        <v>240</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" s="108" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="111" t="s">
-        <v>228</v>
-      </c>
-      <c r="B20" s="111" t="s">
-        <v>241</v>
-      </c>
-      <c r="C20" s="111" t="s">
-        <v>242</v>
-      </c>
-      <c r="D20" s="108" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="111" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" s="111" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="D21" s="108" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="111" t="s">
-        <v>232</v>
-      </c>
-      <c r="B22" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="C22" s="111" t="s">
-        <v>244</v>
-      </c>
-      <c r="D22" s="108" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="111" t="s">
+      <c r="E29" s="65">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="129" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="167">
+        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Reporte")</f>
+        <v>2</v>
+      </c>
+      <c r="C30" s="168"/>
+      <c r="D30" s="130">
+        <f>(B10+C10)/2</f>
+        <v>450</v>
+      </c>
+      <c r="E30" s="65">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="129" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" s="167">
+        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Seguridad")</f>
+        <v>2</v>
+      </c>
+      <c r="C31" s="168"/>
+      <c r="D31" s="130">
+        <f>(B12+C12)/2</f>
+        <v>750</v>
+      </c>
+      <c r="E31" s="65">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="129" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" s="175">
+        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Consulta")</f>
+        <v>6</v>
+      </c>
+      <c r="C32" s="175"/>
+      <c r="D32" s="130">
+        <f>(B8+C8)/2</f>
+        <v>250</v>
+      </c>
+      <c r="E32" s="65">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="129" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="167">
+        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Integración")</f>
+        <v>2</v>
+      </c>
+      <c r="C33" s="168"/>
+      <c r="D33" s="130">
+        <f>(B11+C11)/2</f>
+        <v>750</v>
+      </c>
+      <c r="E33" s="65">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D34" s="133" t="s">
         <v>234</v>
       </c>
-      <c r="B23" s="111" t="s">
-        <v>244</v>
-      </c>
-      <c r="C23" s="111" t="s">
-        <v>245</v>
-      </c>
-      <c r="D23" s="108" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A25" s="197"/>
-      <c r="B25" s="197"/>
-      <c r="C25" s="197"/>
-      <c r="D25" s="197"/>
-    </row>
-    <row r="26" spans="1:14" ht="22.8" x14ac:dyDescent="0.25">
-      <c r="A26" s="186" t="s">
-        <v>237</v>
-      </c>
-      <c r="B26" s="187"/>
-      <c r="C26" s="187"/>
-      <c r="D26" s="188"/>
-      <c r="J26" s="185" t="s">
-        <v>246</v>
-      </c>
-      <c r="K26" s="185"/>
-      <c r="L26" s="185"/>
-      <c r="M26" s="185"/>
-      <c r="N26" s="185"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="132" t="s">
-        <v>170</v>
-      </c>
-      <c r="B27" s="189" t="s">
-        <v>238</v>
-      </c>
-      <c r="C27" s="190"/>
-      <c r="D27" s="133" t="s">
-        <v>219</v>
-      </c>
-      <c r="E27" s="133" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="130" t="s">
-        <v>179</v>
-      </c>
-      <c r="B28" s="194">
-        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Registro")</f>
-      </c>
-      <c r="C28" s="195"/>
-      <c r="D28" s="131">
-        <f>(B7+C7)/2</f>
-      </c>
-      <c r="E28" s="66">
-        <f>B28*D28</f>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="130" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="194">
-        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Proceso")</f>
-      </c>
-      <c r="C29" s="195"/>
-      <c r="D29" s="131">
-        <f>(B9+C9)/2</f>
-      </c>
-      <c r="E29" s="66">
-        <f>B29*D29</f>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="130" t="s">
-        <v>180</v>
-      </c>
-      <c r="B30" s="194">
-        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Reporte")</f>
-      </c>
-      <c r="C30" s="195"/>
-      <c r="D30" s="131">
-        <f>(B10+C10)/2</f>
-      </c>
-      <c r="E30" s="66">
-        <f>B30*D30</f>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="130" t="s">
-        <v>181</v>
-      </c>
-      <c r="B31" s="194">
-        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Seguridad")</f>
-      </c>
-      <c r="C31" s="195"/>
-      <c r="D31" s="131">
-        <f>(B12+C12)/2</f>
-      </c>
-      <c r="E31" s="66">
-        <f>B31*D31</f>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="130" t="s">
-        <v>192</v>
-      </c>
-      <c r="B32" s="191">
-        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Consulta")</f>
-      </c>
-      <c r="C32" s="191"/>
-      <c r="D32" s="131">
-        <f>(B8+C8)/2</f>
-      </c>
-      <c r="E32" s="66">
-        <f>B32*D32</f>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="130" t="s">
-        <v>207</v>
-      </c>
-      <c r="B33" s="194">
-        <f>COUNTIF('Elementos Funcionales'!$I$15:$I$36,"=Integración")</f>
-      </c>
-      <c r="C33" s="195"/>
-      <c r="D33" s="131">
-        <f>(B11+C11)/2</f>
-      </c>
-      <c r="E33" s="66">
-        <f>B33*D33</f>
-      </c>
-    </row>
-    <row r="34" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D34" s="134" t="s">
-        <v>248</v>
-      </c>
-      <c r="E34" s="135">
+      <c r="E34" s="134">
         <f>SUM(E28:E33)</f>
+        <v>9900</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="J26:N26"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -5016,9 +4913,13 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="J26:N26"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5028,46 +4929,46 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AN88"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.88671875" customWidth="1"/>
-    <col min="14" max="14" width="5.6640625" customWidth="1"/>
-    <col min="15" max="16" width="3.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" customWidth="1"/>
+    <col min="14" max="14" width="5.7109375" customWidth="1"/>
+    <col min="15" max="16" width="3.42578125" customWidth="1"/>
     <col min="17" max="23" width="3" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="4" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="3.33203125" customWidth="1"/>
-    <col min="27" max="27" width="3.109375" customWidth="1"/>
-    <col min="28" max="28" width="3.44140625" customWidth="1"/>
+    <col min="25" max="26" width="3.28515625" customWidth="1"/>
+    <col min="27" max="27" width="3.140625" customWidth="1"/>
+    <col min="28" max="28" width="3.42578125" customWidth="1"/>
     <col min="29" max="29" width="3" customWidth="1"/>
-    <col min="30" max="30" width="3.5546875" customWidth="1"/>
-    <col min="31" max="31" width="3.33203125" customWidth="1"/>
-    <col min="32" max="32" width="3.109375" customWidth="1"/>
-    <col min="33" max="33" width="3.33203125" customWidth="1"/>
-    <col min="34" max="34" width="3.109375" customWidth="1"/>
+    <col min="30" max="30" width="3.5703125" customWidth="1"/>
+    <col min="31" max="31" width="3.28515625" customWidth="1"/>
+    <col min="32" max="32" width="3.140625" customWidth="1"/>
+    <col min="33" max="33" width="3.28515625" customWidth="1"/>
+    <col min="34" max="34" width="3.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
-        <v>160</v>
-      </c>
-      <c r="B1" s="157"/>
+    <row r="1" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="187" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="187"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="158"/>
-      <c r="B2" s="158"/>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="188"/>
+      <c r="B2" s="188"/>
       <c r="C2" s="1"/>
       <c r="D2" s="3"/>
       <c r="E2" s="7"/>
@@ -5081,7 +4982,7 @@
       <c r="M2" s="7"/>
       <c r="N2" s="23"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="16"/>
       <c r="C3" s="1"/>
@@ -5097,7 +4998,7 @@
       <c r="M3" s="7"/>
       <c r="N3" s="23"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="42" t="s">
         <v>62</v>
       </c>
@@ -5115,7 +5016,7 @@
       <c r="M4" s="24"/>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="16"/>
       <c r="C5" s="1"/>
@@ -5131,7 +5032,7 @@
       <c r="M5" s="26"/>
       <c r="N5" s="23"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>1</v>
       </c>
@@ -5149,7 +5050,7 @@
       <c r="M6" s="26"/>
       <c r="N6" s="23"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="16"/>
       <c r="C7" s="1"/>
@@ -5165,7 +5066,7 @@
       <c r="M7" s="26"/>
       <c r="N7" s="23"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -5183,7 +5084,7 @@
       <c r="M8" s="22"/>
       <c r="N8" s="23"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -5201,7 +5102,7 @@
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -5219,78 +5120,79 @@
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="85" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="86">
+    <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="84" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="85">
         <f>'Tabla cálculo LOC'!B3</f>
-      </c>
-      <c r="C12" s="151" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" s="151"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>9.9</v>
+      </c>
+      <c r="C12" s="182" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="182"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="16"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>60</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
         <v>67</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="16"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:34" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="16"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="72"/>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="D18" s="71"/>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" s="19"/>
       <c r="B19" s="16"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" s="19"/>
       <c r="B20" s="16"/>
       <c r="C20" s="33"/>
-      <c r="D20" s="54"/>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="D20" s="53"/>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" s="19"/>
       <c r="B21" s="16"/>
       <c r="C21" s="33"/>
-      <c r="D21" s="54"/>
+      <c r="D21" s="53"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
@@ -5305,11 +5207,11 @@
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="16"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="54"/>
+      <c r="D22" s="53"/>
       <c r="O22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
@@ -5324,24 +5226,24 @@
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
     </row>
-    <row r="24" spans="1:34" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A24" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="62"/>
+    <row r="24" spans="1:34" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="61"/>
       <c r="C24" s="33"/>
       <c r="O24" s="37" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" s="38" t="s">
         <v>66</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="91" t="s">
-        <v>253</v>
+      <c r="D25" s="90" t="s">
+        <v>239</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -5350,36 +5252,36 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="8"/>
-      <c r="L25" s="79"/>
+      <c r="L25" s="78"/>
       <c r="M25" s="7"/>
-      <c r="O25" s="152" t="s">
-        <v>100</v>
-      </c>
-      <c r="P25" s="153"/>
-      <c r="Q25" s="153"/>
-      <c r="R25" s="153"/>
-      <c r="S25" s="153"/>
-      <c r="T25" s="153"/>
-      <c r="U25" s="153"/>
-      <c r="V25" s="153"/>
-      <c r="W25" s="153"/>
-      <c r="X25" s="153"/>
-      <c r="Y25" s="153"/>
-      <c r="Z25" s="153"/>
-      <c r="AA25" s="153"/>
-      <c r="AB25" s="153"/>
-      <c r="AC25" s="153"/>
-      <c r="AD25" s="153"/>
-      <c r="AE25" s="153"/>
-      <c r="AF25" s="153"/>
-      <c r="AG25" s="153"/>
-      <c r="AH25" s="154"/>
-    </row>
-    <row r="26" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="155" t="s">
+      <c r="O25" s="183" t="s">
+        <v>87</v>
+      </c>
+      <c r="P25" s="184"/>
+      <c r="Q25" s="184"/>
+      <c r="R25" s="184"/>
+      <c r="S25" s="184"/>
+      <c r="T25" s="184"/>
+      <c r="U25" s="184"/>
+      <c r="V25" s="184"/>
+      <c r="W25" s="184"/>
+      <c r="X25" s="184"/>
+      <c r="Y25" s="184"/>
+      <c r="Z25" s="184"/>
+      <c r="AA25" s="184"/>
+      <c r="AB25" s="184"/>
+      <c r="AC25" s="184"/>
+      <c r="AD25" s="184"/>
+      <c r="AE25" s="184"/>
+      <c r="AF25" s="184"/>
+      <c r="AG25" s="184"/>
+      <c r="AH25" s="185"/>
+    </row>
+    <row r="26" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="160" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="156"/>
+      <c r="B26" s="186"/>
       <c r="C26" s="4"/>
       <c r="D26" s="35" t="s">
         <v>58</v>
@@ -5406,214 +5308,232 @@
         <v>7</v>
       </c>
       <c r="L26" s="35" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O26" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="P26" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q26" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="R26" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="S26" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="T26" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="U26" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="V26" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="W26" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="X26" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y26" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z26" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA26" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB26" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="P26" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q26" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="R26" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="S26" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="T26" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="U26" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="V26" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="W26" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="X26" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y26" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z26" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA26" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB26" s="39" t="s">
-        <v>124</v>
-      </c>
       <c r="AC26" s="39" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="AD26" s="39" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="AE26" s="39" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="AF26" s="39" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="AG26" s="39" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="AH26" s="39" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:34" s="7" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" s="7" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A27" s="29" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="B27" s="30">
         <f>'Elementos Funcionales'!G10</f>
+        <v>22</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" s="50">
+        <v>117</v>
+      </c>
+      <c r="E27" s="49">
         <v>1</v>
       </c>
-      <c r="F27" s="82">
+      <c r="F27" s="81">
         <f>COUNTIF($O$27:$AH$27,"=D")/$E$35</f>
-      </c>
-      <c r="G27" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="G27" s="81">
         <f>COUNTIF($O$27:$AH$27,"=C")/$E$35</f>
-      </c>
-      <c r="H27" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="H27" s="81">
         <f>COUNTIF($O$27:$AH$27,"=P")/$E$35</f>
-      </c>
-      <c r="I27" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="I27" s="81">
         <f>COUNTIF($O$27:$AH$27,"=I")/$E$35</f>
-      </c>
-      <c r="J27" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="J27" s="81">
         <f>SUM(F27:I27)</f>
-      </c>
-      <c r="K27" s="82">
+        <v>0.2</v>
+      </c>
+      <c r="K27" s="81">
         <f>E27*J27</f>
-      </c>
-      <c r="L27" s="87">
+        <v>0.2</v>
+      </c>
+      <c r="L27" s="86">
         <f>J27*$B$35</f>
-      </c>
-      <c r="M27" s="77">
+        <v>4140.7801813170072</v>
+      </c>
+      <c r="M27" s="76">
         <f>K27*L27</f>
+        <v>828.15603626340146</v>
       </c>
       <c r="N27" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="O27" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="O27" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="71" t="s">
+      <c r="P27" s="70"/>
+      <c r="Q27" s="70"/>
+      <c r="R27" s="70"/>
+      <c r="S27" s="70"/>
+      <c r="T27" s="70"/>
+      <c r="U27" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="V27" s="71"/>
-      <c r="W27" s="71"/>
-      <c r="X27" s="71"/>
-      <c r="Y27" s="71"/>
-      <c r="Z27" s="71"/>
-      <c r="AA27" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB27" s="71"/>
-      <c r="AC27" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD27" s="71"/>
-      <c r="AE27" s="71"/>
-      <c r="AF27" s="71"/>
-      <c r="AG27" s="71"/>
-      <c r="AH27" s="71"/>
-    </row>
-    <row r="28" spans="1:34" s="7" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
+      <c r="V27" s="70"/>
+      <c r="W27" s="70"/>
+      <c r="X27" s="70"/>
+      <c r="Y27" s="70"/>
+      <c r="Z27" s="70"/>
+      <c r="AA27" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB27" s="70"/>
+      <c r="AC27" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD27" s="70"/>
+      <c r="AE27" s="70"/>
+      <c r="AF27" s="70"/>
+      <c r="AG27" s="70"/>
+      <c r="AH27" s="70"/>
+    </row>
+    <row r="28" spans="1:34" s="7" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A28" s="29" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B28" s="30">
         <f>'Elementos Funcionales'!F10</f>
+        <v>90</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="50">
+        <v>118</v>
+      </c>
+      <c r="E28" s="49">
         <v>1</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F28" s="81">
         <f>COUNTIF($O$28:$AH$28,"=D")/$E$35</f>
-      </c>
-      <c r="G28" s="82">
+        <v>0.1</v>
+      </c>
+      <c r="G28" s="81">
         <f>COUNTIF($O$28:$AH$28,"=C")/$E$35</f>
-      </c>
-      <c r="H28" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="H28" s="81">
         <f>COUNTIF($O$28:$AH$28,"=P")/$E$35</f>
-      </c>
-      <c r="I28" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="I28" s="81">
         <f>COUNTIF($O$28:$AH$28,"=I")/$E$35</f>
-      </c>
-      <c r="J28" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="J28" s="81">
         <f>SUM(F28:I28)</f>
-      </c>
-      <c r="K28" s="82">
+        <v>0.25</v>
+      </c>
+      <c r="K28" s="81">
         <f>E28*J28</f>
-      </c>
-      <c r="L28" s="87">
+        <v>0.25</v>
+      </c>
+      <c r="L28" s="86">
         <f>J28*$B$35</f>
-      </c>
-      <c r="M28" s="77">
+        <v>5175.9752266462583</v>
+      </c>
+      <c r="M28" s="76">
         <f>K28*L28</f>
+        <v>1293.9938066615646</v>
       </c>
       <c r="N28" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="O28" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="O28" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="P28" s="71" t="s">
+      <c r="P28" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="Q28" s="71"/>
-      <c r="R28" s="71"/>
-      <c r="S28" s="71" t="s">
+      <c r="Q28" s="70"/>
+      <c r="R28" s="70"/>
+      <c r="S28" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="T28" s="71"/>
-      <c r="U28" s="71"/>
-      <c r="V28" s="71"/>
-      <c r="W28" s="71"/>
-      <c r="X28" s="71"/>
-      <c r="Y28" s="71"/>
-      <c r="Z28" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA28" s="71"/>
-      <c r="AB28" s="71"/>
-      <c r="AC28" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD28" s="71"/>
-      <c r="AE28" s="71"/>
-      <c r="AF28" s="71"/>
-      <c r="AG28" s="71"/>
-      <c r="AH28" s="71"/>
-    </row>
-    <row r="29" spans="1:34" s="7" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
+      <c r="T28" s="70"/>
+      <c r="U28" s="70"/>
+      <c r="V28" s="70"/>
+      <c r="W28" s="70"/>
+      <c r="X28" s="70"/>
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA28" s="70"/>
+      <c r="AB28" s="70"/>
+      <c r="AC28" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD28" s="70"/>
+      <c r="AE28" s="70"/>
+      <c r="AF28" s="70"/>
+      <c r="AG28" s="70"/>
+      <c r="AH28" s="70"/>
+    </row>
+    <row r="29" spans="1:34" s="7" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A29" s="29" t="s">
         <v>8</v>
       </c>
@@ -5621,257 +5541,287 @@
         <v>2.94</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" s="50">
+        <v>119</v>
+      </c>
+      <c r="E29" s="49">
         <v>1</v>
       </c>
-      <c r="F29" s="82">
+      <c r="F29" s="81">
         <f>COUNTIF($O$29:$AH$29,"=D")/$E$35</f>
-      </c>
-      <c r="G29" s="82">
+        <v>0.15</v>
+      </c>
+      <c r="G29" s="81">
         <f>COUNTIF($O$29:$AH$29,"=C")/$E$35</f>
-      </c>
-      <c r="H29" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="H29" s="81">
         <f>COUNTIF($O$29:$AH$29,"=P")/$E$35</f>
-      </c>
-      <c r="I29" s="82">
+        <v>0</v>
+      </c>
+      <c r="I29" s="81">
         <f>COUNTIF($O$29:$AH$29,"=I")/$E$35</f>
-      </c>
-      <c r="J29" s="82">
+        <v>0.1</v>
+      </c>
+      <c r="J29" s="81">
         <f>SUM(F29:I29)</f>
-      </c>
-      <c r="K29" s="82">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="K29" s="81">
         <f>E29*J29</f>
-      </c>
-      <c r="L29" s="87">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="L29" s="86">
         <f t="shared" ref="L29:L31" si="0">J29*$B$35</f>
-      </c>
-      <c r="M29" s="77">
+        <v>6211.1702719755112</v>
+      </c>
+      <c r="M29" s="76">
         <f>K29*L29</f>
+        <v>1863.3510815926536</v>
       </c>
       <c r="N29" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="O29" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="O29" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="P29" s="71" t="s">
+      <c r="P29" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="Q29" s="71" t="s">
+      <c r="Q29" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="R29" s="69" t="s">
+      <c r="R29" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="S29" s="71"/>
-      <c r="T29" s="69"/>
-      <c r="U29" s="69"/>
-      <c r="V29" s="69"/>
-      <c r="W29" s="69"/>
-      <c r="X29" s="69"/>
-      <c r="Y29" s="71"/>
-      <c r="Z29" s="71"/>
-      <c r="AA29" s="71"/>
-      <c r="AB29" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC29" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="AD29" s="69"/>
-      <c r="AE29" s="71"/>
-      <c r="AF29" s="69"/>
-      <c r="AG29" s="69"/>
-      <c r="AH29" s="69"/>
-    </row>
-    <row r="30" spans="1:34" s="7" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
+      <c r="S29" s="70"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="68"/>
+      <c r="Y29" s="70"/>
+      <c r="Z29" s="70"/>
+      <c r="AA29" s="70"/>
+      <c r="AB29" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC29" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD29" s="68"/>
+      <c r="AE29" s="70"/>
+      <c r="AF29" s="68"/>
+      <c r="AG29" s="68"/>
+      <c r="AH29" s="68"/>
+    </row>
+    <row r="30" spans="1:34" s="7" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A30" s="29" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="36">
         <f>B12</f>
+        <v>9.9</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" s="50">
+        <v>120</v>
+      </c>
+      <c r="E30" s="49">
         <v>1</v>
       </c>
-      <c r="F30" s="82">
+      <c r="F30" s="81">
         <f>COUNTIF($O$30:$AH$30,"=D")/$E$35</f>
-      </c>
-      <c r="G30" s="82">
+        <v>0.1</v>
+      </c>
+      <c r="G30" s="81">
         <f>COUNTIF($O$30:$AH$30,"=C")/$E$35</f>
-      </c>
-      <c r="H30" s="82">
+        <v>0.35</v>
+      </c>
+      <c r="H30" s="81">
         <f>COUNTIF($O$30:$AH$30,"=P")/$E$35</f>
-      </c>
-      <c r="I30" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="I30" s="81">
         <f>COUNTIF($O$30:$AH$30,"=I")/$E$35</f>
-      </c>
-      <c r="J30" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="J30" s="81">
         <f>SUM(F30:I30)</f>
-      </c>
-      <c r="K30" s="82">
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="K30" s="81">
         <f>E30*J30</f>
-      </c>
-      <c r="L30" s="87">
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="L30" s="86">
         <f t="shared" si="0"/>
-      </c>
-      <c r="M30" s="77">
+        <v>11387.145498621767</v>
+      </c>
+      <c r="M30" s="76">
         <f>K30*L30</f>
+        <v>6262.9300242419713</v>
       </c>
       <c r="N30" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="O30" s="70"/>
+      <c r="P30" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="Q30" s="71" t="s">
+      <c r="Q30" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="R30" s="71" t="s">
+      <c r="R30" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="S30" s="71" t="s">
+      <c r="S30" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="T30" s="71" t="s">
+      <c r="T30" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="U30" s="71" t="s">
+      <c r="U30" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="V30" s="71" t="s">
+      <c r="V30" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="W30" s="71" t="s">
+      <c r="W30" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="X30" s="71" t="s">
+      <c r="X30" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="Y30" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="Z30" s="71"/>
-      <c r="AA30" s="71"/>
-      <c r="AB30" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC30" s="71"/>
-      <c r="AD30" s="71"/>
-      <c r="AE30" s="71"/>
-      <c r="AF30" s="71"/>
-      <c r="AG30" s="71"/>
-      <c r="AH30" s="71"/>
-    </row>
-    <row r="31" spans="1:34" s="7" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
+      <c r="Y30" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z30" s="70"/>
+      <c r="AA30" s="70"/>
+      <c r="AB30" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC30" s="70"/>
+      <c r="AD30" s="70"/>
+      <c r="AE30" s="70"/>
+      <c r="AF30" s="70"/>
+      <c r="AG30" s="70"/>
+      <c r="AH30" s="70"/>
+    </row>
+    <row r="31" spans="1:34" s="7" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A31" s="29" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="30">
         <f>'Factores Complejidad Tecnica'!$E$16</f>
+        <v>1.105</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" s="50">
+        <v>121</v>
+      </c>
+      <c r="E31" s="49">
         <v>1</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="81">
         <f>COUNTIF($O$31:$AH$31,"=D")/$E$35</f>
-      </c>
-      <c r="G31" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="G31" s="81">
         <f>COUNTIF($O$31:$AH$31,"=C")/$E$35</f>
-      </c>
-      <c r="H31" s="82">
+        <v>0</v>
+      </c>
+      <c r="H31" s="81">
         <f>COUNTIF($O$31:$AH$31,"=P")/$E$35</f>
-      </c>
-      <c r="I31" s="82">
+        <v>0.25</v>
+      </c>
+      <c r="I31" s="81">
         <f>COUNTIF($O$31:$AH$31,"=I")/$E$35</f>
-      </c>
-      <c r="J31" s="82">
+        <v>0.05</v>
+      </c>
+      <c r="J31" s="81">
         <f>SUM(F31:I31)</f>
-      </c>
-      <c r="K31" s="82">
+        <v>0.35</v>
+      </c>
+      <c r="K31" s="81">
         <f>E31*J31</f>
-      </c>
-      <c r="L31" s="87">
+        <v>0.35</v>
+      </c>
+      <c r="L31" s="86">
         <f t="shared" si="0"/>
-      </c>
-      <c r="M31" s="77">
+        <v>7246.3653173047614</v>
+      </c>
+      <c r="M31" s="76">
         <f>K31*L31</f>
+        <v>2536.2278610566664</v>
       </c>
       <c r="N31" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="O31" s="70"/>
+      <c r="P31" s="70"/>
+      <c r="Q31" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="71"/>
-      <c r="V31" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="W31" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="X31" s="71"/>
-      <c r="Y31" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="Z31" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA31" s="71" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB31" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC31" s="71"/>
-      <c r="AD31" s="71"/>
-      <c r="AE31" s="71"/>
-      <c r="AF31" s="71"/>
-      <c r="AG31" s="71"/>
-      <c r="AH31" s="71"/>
-    </row>
-    <row r="32" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R31" s="70"/>
+      <c r="S31" s="70"/>
+      <c r="T31" s="70"/>
+      <c r="U31" s="70"/>
+      <c r="V31" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="W31" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="X31" s="70"/>
+      <c r="Y31" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z31" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA31" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB31" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC31" s="70"/>
+      <c r="AD31" s="70"/>
+      <c r="AE31" s="70"/>
+      <c r="AF31" s="70"/>
+      <c r="AG31" s="70"/>
+      <c r="AH31" s="70"/>
+    </row>
+    <row r="32" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="29" t="s">
         <v>10</v>
       </c>
       <c r="B32" s="30">
         <f>B28*B30/1000</f>
+        <v>0.89100000000000001</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="E32" s="74">
+      <c r="E32" s="73">
         <f>SUM(E27:E31)</f>
-      </c>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="75">
+        <v>5</v>
+      </c>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="74">
         <f>SUM(K27:K31)</f>
+        <v>1.65</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="M32" s="78">
+        <v>152</v>
+      </c>
+      <c r="M32" s="77">
         <f>SUM(M27:M31)</f>
-      </c>
-      <c r="O32" s="90" t="s">
+        <v>12784.658809816257</v>
+      </c>
+      <c r="O32" s="89" t="s">
         <v>40</v>
       </c>
       <c r="P32" s="7" t="s">
@@ -5888,12 +5838,13 @@
       <c r="AG32"/>
       <c r="AH32"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="31" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B33" s="32">
         <f>B29*POWER(B32,B31)</f>
+        <v>2.5879876133231288</v>
       </c>
       <c r="D33" s="18"/>
       <c r="E33" s="3"/>
@@ -5902,7 +5853,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="68"/>
+      <c r="K33" s="67"/>
       <c r="L33" s="21"/>
       <c r="M33" s="22"/>
       <c r="N33" s="7"/>
@@ -5923,32 +5874,32 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="83">
+        <v>68</v>
+      </c>
+      <c r="B34" s="82">
         <v>50</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" s="88">
+        <v>90</v>
+      </c>
+      <c r="E34" s="87">
         <v>4</v>
       </c>
-      <c r="F34" s="89" t="s">
-        <v>106</v>
+      <c r="F34" s="88" t="s">
+        <v>93</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="N34" s="7"/>
-      <c r="O34" s="80" t="s">
-        <v>140</v>
+      <c r="O34" s="79" t="s">
+        <v>127</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
@@ -5961,70 +5912,71 @@
       <c r="Y34" s="7"/>
       <c r="Z34" s="7"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="B35" s="83">
+        <v>240</v>
+      </c>
+      <c r="B35" s="82">
         <f>B34*B33*E35*E37</f>
+        <v>20703.900906585033</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="50">
+        <v>89</v>
+      </c>
+      <c r="E35" s="49">
         <v>20</v>
       </c>
-      <c r="F35" s="51" t="s">
-        <v>107</v>
+      <c r="F35" s="50" t="s">
+        <v>94</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
-      <c r="L35" s="67"/>
+      <c r="L35" s="66"/>
       <c r="N35" s="7"/>
-      <c r="O35" s="81" t="s">
-        <v>141</v>
+      <c r="O35" s="80" t="s">
+        <v>128</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="50">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D36" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="E36" s="49">
         <v>5</v>
       </c>
-      <c r="F36" s="51" t="s">
-        <v>107</v>
+      <c r="F36" s="50" t="s">
+        <v>94</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:26" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="159" t="s">
-        <v>252</v>
-      </c>
-      <c r="B37" s="159"/>
-      <c r="D37" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" s="50">
+    <row r="37" spans="1:26" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="189" t="s">
+        <v>238</v>
+      </c>
+      <c r="B37" s="189"/>
+      <c r="D37" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="49">
         <v>8</v>
       </c>
-      <c r="F37" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="G37" s="76"/>
+      <c r="F37" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37" s="75"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="N37" s="7"/>
-      <c r="O37" s="69"/>
+      <c r="O37" s="68"/>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
@@ -6037,7 +5989,7 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="D38" s="7"/>
@@ -6046,10 +5998,10 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="73"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="72"/>
       <c r="N38" s="7"/>
-      <c r="O38" s="70"/>
+      <c r="O38" s="69"/>
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
@@ -6062,664 +6014,664 @@
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
     </row>
-    <row r="39" spans="1:26" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="D39" s="164" t="s">
+    <row r="39" spans="1:26" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="D39" s="194" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" s="194"/>
+      <c r="F39" s="194"/>
+      <c r="G39" s="194"/>
+      <c r="H39" s="194"/>
+      <c r="I39" s="194"/>
+      <c r="J39" s="194"/>
+      <c r="K39" s="194"/>
+      <c r="L39" s="194"/>
+      <c r="M39" s="194"/>
+      <c r="N39" s="194"/>
+      <c r="O39" s="194"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D40" s="128"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D41" s="135" t="s">
+        <v>242</v>
+      </c>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D42" s="135" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D43" s="135" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D44" s="135" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D45" s="125"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D46" s="135" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D47" s="135" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="D48" s="135" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="49" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D49" s="135" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="50" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D50" s="128"/>
+    </row>
+    <row r="51" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D51" s="135" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="52" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D52" s="135" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="53" spans="4:40" ht="31.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D53" s="196" t="s">
+        <v>281</v>
+      </c>
+      <c r="E53" s="196"/>
+      <c r="F53" s="196"/>
+      <c r="G53" s="196"/>
+      <c r="H53" s="196"/>
+      <c r="I53" s="196"/>
+      <c r="J53" s="196"/>
+      <c r="K53" s="196"/>
+      <c r="L53" s="196"/>
+      <c r="M53" s="196"/>
+      <c r="N53" s="196"/>
+      <c r="O53" s="196"/>
+      <c r="P53" s="196"/>
+      <c r="Q53" s="196"/>
+      <c r="R53" s="196"/>
+      <c r="S53" s="196"/>
+      <c r="T53" s="196"/>
+      <c r="U53" s="196"/>
+      <c r="V53" s="196"/>
+      <c r="W53" s="196"/>
+      <c r="X53" s="196"/>
+      <c r="Y53" s="196"/>
+      <c r="Z53" s="196"/>
+      <c r="AA53" s="196"/>
+      <c r="AB53" s="196"/>
+      <c r="AC53" s="196"/>
+      <c r="AD53" s="196"/>
+    </row>
+    <row r="54" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D54" s="135" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="55" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D55" s="128"/>
+    </row>
+    <row r="56" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D56" s="135" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="57" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D57" s="135" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="58" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D58" s="135" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="59" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D59" s="135" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="60" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D60" s="128"/>
+    </row>
+    <row r="61" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D61" s="135" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="62" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D62" s="135" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="63" spans="4:40" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D63" s="195" t="s">
+        <v>287</v>
+      </c>
+      <c r="E63" s="195"/>
+      <c r="F63" s="195"/>
+      <c r="G63" s="195"/>
+      <c r="H63" s="195"/>
+      <c r="I63" s="195"/>
+      <c r="J63" s="195"/>
+      <c r="K63" s="195"/>
+      <c r="L63" s="195"/>
+      <c r="M63" s="195"/>
+      <c r="N63" s="195"/>
+      <c r="O63" s="195"/>
+      <c r="P63" s="195"/>
+      <c r="Q63" s="195"/>
+      <c r="R63" s="195"/>
+      <c r="S63" s="195"/>
+      <c r="T63" s="195"/>
+      <c r="U63" s="195"/>
+      <c r="V63" s="195"/>
+      <c r="W63" s="195"/>
+      <c r="X63" s="195"/>
+      <c r="Y63" s="135"/>
+      <c r="Z63" s="135"/>
+      <c r="AA63" s="135"/>
+      <c r="AB63" s="135"/>
+      <c r="AC63" s="135"/>
+      <c r="AD63" s="135"/>
+      <c r="AE63" s="135"/>
+      <c r="AF63" s="135"/>
+      <c r="AG63" s="135"/>
+      <c r="AH63" s="135"/>
+      <c r="AI63" s="135"/>
+      <c r="AJ63" s="135"/>
+      <c r="AK63" s="135"/>
+      <c r="AL63" s="135"/>
+      <c r="AM63" s="135"/>
+      <c r="AN63" s="135"/>
+    </row>
+    <row r="64" spans="4:40" x14ac:dyDescent="0.2">
+      <c r="D64" s="135" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B67" s="90" t="s">
+        <v>247</v>
+      </c>
+      <c r="D67" s="190" t="s">
+        <v>289</v>
+      </c>
+      <c r="E67" s="190"/>
+      <c r="F67" s="190"/>
+      <c r="G67" s="190"/>
+      <c r="H67" s="190"/>
+      <c r="I67" s="190"/>
+      <c r="J67" s="190"/>
+      <c r="K67" s="190"/>
+      <c r="L67" s="190"/>
+      <c r="M67" s="190"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="D68" s="190"/>
+      <c r="E68" s="190"/>
+      <c r="F68" s="190"/>
+      <c r="G68" s="190"/>
+      <c r="H68" s="190"/>
+      <c r="I68" s="190"/>
+      <c r="J68" s="190"/>
+      <c r="K68" s="190"/>
+      <c r="L68" s="190"/>
+      <c r="M68" s="190"/>
+    </row>
+    <row r="69" spans="2:29" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D69" s="190"/>
+      <c r="E69" s="190"/>
+      <c r="F69" s="190"/>
+      <c r="G69" s="190"/>
+      <c r="H69" s="190"/>
+      <c r="I69" s="190"/>
+      <c r="J69" s="190"/>
+      <c r="K69" s="190"/>
+      <c r="L69" s="190"/>
+      <c r="M69" s="190"/>
+    </row>
+    <row r="75" spans="2:29" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="B75" s="193" t="s">
+        <v>248</v>
+      </c>
+      <c r="C75" s="193"/>
+      <c r="D75" s="193"/>
+      <c r="E75" s="193"/>
+      <c r="F75" s="193"/>
+      <c r="G75" s="193"/>
+      <c r="H75" s="193"/>
+      <c r="I75" s="193"/>
+      <c r="J75" s="193"/>
+      <c r="K75" s="193"/>
+      <c r="L75" s="193"/>
+      <c r="M75" s="193"/>
+      <c r="N75" s="193"/>
+      <c r="O75" s="193"/>
+      <c r="P75" s="193"/>
+      <c r="Q75" s="193"/>
+      <c r="R75" s="193"/>
+      <c r="S75" s="193"/>
+      <c r="T75" s="193"/>
+      <c r="U75" s="193"/>
+      <c r="V75" s="193"/>
+      <c r="W75" s="193"/>
+      <c r="X75" s="193"/>
+      <c r="Y75" s="193"/>
+      <c r="Z75" s="193"/>
+      <c r="AA75" s="193"/>
+      <c r="AB75" s="136"/>
+      <c r="AC75" s="136"/>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B76" s="136"/>
+      <c r="C76" s="136"/>
+      <c r="D76" s="136"/>
+      <c r="E76" s="136"/>
+      <c r="F76" s="136"/>
+      <c r="G76" s="136"/>
+      <c r="H76" s="136"/>
+      <c r="I76" s="136"/>
+      <c r="J76" s="136"/>
+      <c r="K76" s="136"/>
+      <c r="L76" s="136"/>
+      <c r="M76" s="136"/>
+      <c r="N76" s="136"/>
+      <c r="O76" s="136"/>
+      <c r="P76" s="136"/>
+      <c r="Q76" s="136"/>
+      <c r="R76" s="136"/>
+      <c r="S76" s="136"/>
+      <c r="T76" s="136"/>
+      <c r="U76" s="136"/>
+      <c r="V76" s="136"/>
+      <c r="W76" s="136"/>
+      <c r="X76" s="136"/>
+      <c r="Y76" s="136"/>
+      <c r="Z76" s="136"/>
+      <c r="AA76" s="136"/>
+      <c r="AB76" s="136"/>
+      <c r="AC76" s="136"/>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B77" s="136" t="s">
+        <v>249</v>
+      </c>
+      <c r="C77" s="136"/>
+      <c r="D77" s="136"/>
+      <c r="E77" s="136"/>
+      <c r="F77" s="136"/>
+      <c r="G77" s="136"/>
+      <c r="H77" s="136"/>
+      <c r="I77" s="136"/>
+      <c r="J77" s="136"/>
+      <c r="K77" s="136"/>
+      <c r="L77" s="136"/>
+      <c r="M77" s="136"/>
+      <c r="N77" s="136"/>
+      <c r="O77" s="136"/>
+      <c r="P77" s="136"/>
+      <c r="Q77" s="136"/>
+      <c r="R77" s="136"/>
+      <c r="S77" s="136"/>
+      <c r="T77" s="136"/>
+      <c r="U77" s="136"/>
+      <c r="V77" s="136"/>
+      <c r="W77" s="136"/>
+      <c r="X77" s="136"/>
+      <c r="Y77" s="136"/>
+      <c r="Z77" s="136"/>
+      <c r="AA77" s="136"/>
+      <c r="AB77" s="136"/>
+      <c r="AC77" s="136"/>
+    </row>
+    <row r="78" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B78" s="136"/>
+      <c r="C78" s="136"/>
+      <c r="D78" s="136"/>
+      <c r="E78" s="136"/>
+      <c r="F78" s="136"/>
+      <c r="G78" s="136"/>
+      <c r="H78" s="136"/>
+      <c r="I78" s="136"/>
+      <c r="J78" s="136"/>
+      <c r="K78" s="136"/>
+      <c r="L78" s="136"/>
+      <c r="M78" s="136"/>
+      <c r="N78" s="136"/>
+      <c r="O78" s="136"/>
+      <c r="P78" s="136"/>
+      <c r="Q78" s="136"/>
+      <c r="R78" s="136"/>
+      <c r="S78" s="136"/>
+      <c r="T78" s="136"/>
+      <c r="U78" s="136"/>
+      <c r="V78" s="136"/>
+      <c r="W78" s="136"/>
+      <c r="X78" s="136"/>
+      <c r="Y78" s="136"/>
+      <c r="Z78" s="136"/>
+      <c r="AA78" s="136"/>
+      <c r="AB78" s="136"/>
+      <c r="AC78" s="136"/>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B79" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="C79" s="192"/>
+      <c r="D79" s="192"/>
+      <c r="E79" s="192"/>
+      <c r="F79" s="192"/>
+      <c r="G79" s="192"/>
+      <c r="H79" s="192"/>
+      <c r="I79" s="192"/>
+      <c r="J79" s="192"/>
+      <c r="K79" s="192"/>
+      <c r="L79" s="192"/>
+      <c r="M79" s="192"/>
+      <c r="N79" s="192"/>
+      <c r="O79" s="192"/>
+      <c r="P79" s="192"/>
+      <c r="Q79" s="136"/>
+      <c r="R79" s="136"/>
+      <c r="S79" s="136"/>
+      <c r="T79" s="136"/>
+      <c r="U79" s="136"/>
+      <c r="V79" s="136"/>
+      <c r="W79" s="136"/>
+      <c r="X79" s="136"/>
+      <c r="Y79" s="136"/>
+      <c r="Z79" s="136"/>
+      <c r="AA79" s="136"/>
+      <c r="AB79" s="136"/>
+      <c r="AC79" s="136"/>
+    </row>
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B80" s="192"/>
+      <c r="C80" s="192"/>
+      <c r="D80" s="192"/>
+      <c r="E80" s="192"/>
+      <c r="F80" s="192"/>
+      <c r="G80" s="192"/>
+      <c r="H80" s="192"/>
+      <c r="I80" s="192"/>
+      <c r="J80" s="192"/>
+      <c r="K80" s="192"/>
+      <c r="L80" s="192"/>
+      <c r="M80" s="192"/>
+      <c r="N80" s="192"/>
+      <c r="O80" s="192"/>
+      <c r="P80" s="192"/>
+      <c r="Q80" s="136"/>
+      <c r="R80" s="136"/>
+      <c r="S80" s="136"/>
+      <c r="T80" s="136"/>
+      <c r="U80" s="136"/>
+      <c r="V80" s="136"/>
+      <c r="W80" s="136"/>
+      <c r="X80" s="136"/>
+      <c r="Y80" s="136"/>
+      <c r="Z80" s="136"/>
+      <c r="AA80" s="136"/>
+      <c r="AB80" s="136"/>
+      <c r="AC80" s="136"/>
+    </row>
+    <row r="81" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B81" s="137" t="s">
         <v>255</v>
       </c>
-      <c r="E39" s="164"/>
-      <c r="F39" s="164"/>
-      <c r="G39" s="164"/>
-      <c r="H39" s="164"/>
-      <c r="I39" s="164"/>
-      <c r="J39" s="164"/>
-      <c r="K39" s="164"/>
-      <c r="L39" s="164"/>
-      <c r="M39" s="164"/>
-      <c r="N39" s="164"/>
-      <c r="O39" s="164"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="129"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="136" t="s">
-        <v>256</v>
-      </c>
-      <c r="H41" s="72"/>
-      <c r="I41" s="72"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="136" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D43" s="136" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D44" s="136" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D45" s="126"/>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D46" s="136" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D47" s="136" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D48" s="136" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="49" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D49" s="136" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="50" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D50" s="129"/>
-    </row>
-    <row r="51" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D51" s="136" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="52" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D52" s="136" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="53" spans="4:40" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="220" t="s">
-        <v>309</v>
-      </c>
-      <c r="E53" s="220"/>
-      <c r="F53" s="220"/>
-      <c r="G53" s="220"/>
-      <c r="H53" s="220"/>
-      <c r="I53" s="220"/>
-      <c r="J53" s="220"/>
-      <c r="K53" s="220"/>
-      <c r="L53" s="220"/>
-      <c r="M53" s="220"/>
-      <c r="N53" s="220"/>
-      <c r="O53" s="220"/>
-      <c r="P53" s="220"/>
-      <c r="Q53" s="220"/>
-      <c r="R53" s="220"/>
-      <c r="S53" s="220"/>
-      <c r="T53" s="220"/>
-      <c r="U53" s="220"/>
-      <c r="V53" s="220"/>
-      <c r="W53" s="220"/>
-      <c r="X53" s="220"/>
-      <c r="Y53" s="220"/>
-      <c r="Z53" s="220"/>
-      <c r="AA53" s="220"/>
-      <c r="AB53" s="220"/>
-      <c r="AC53" s="220"/>
-      <c r="AD53" s="220"/>
-    </row>
-    <row r="54" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D54" s="136" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="55" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D55" s="129"/>
-    </row>
-    <row r="56" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D56" s="136" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="57" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D57" s="136" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="58" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D58" s="136" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="59" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D59" s="136" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="60" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D60" s="129"/>
-    </row>
-    <row r="61" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D61" s="136" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="62" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D62" s="136" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="63" spans="4:40" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="219" t="s">
-        <v>315</v>
-      </c>
-      <c r="E63" s="219"/>
-      <c r="F63" s="219"/>
-      <c r="G63" s="219"/>
-      <c r="H63" s="219"/>
-      <c r="I63" s="219"/>
-      <c r="J63" s="219"/>
-      <c r="K63" s="219"/>
-      <c r="L63" s="219"/>
-      <c r="M63" s="219"/>
-      <c r="N63" s="219"/>
-      <c r="O63" s="219"/>
-      <c r="P63" s="219"/>
-      <c r="Q63" s="219"/>
-      <c r="R63" s="219"/>
-      <c r="S63" s="219"/>
-      <c r="T63" s="219"/>
-      <c r="U63" s="219"/>
-      <c r="V63" s="219"/>
-      <c r="W63" s="219"/>
-      <c r="X63" s="219"/>
-      <c r="Y63" s="136"/>
-      <c r="Z63" s="136"/>
-      <c r="AA63" s="136"/>
-      <c r="AB63" s="136"/>
-      <c r="AC63" s="136"/>
-      <c r="AD63" s="136"/>
-      <c r="AE63" s="136"/>
-      <c r="AF63" s="136"/>
-      <c r="AG63" s="136"/>
-      <c r="AH63" s="136"/>
-      <c r="AI63" s="136"/>
-      <c r="AJ63" s="136"/>
-      <c r="AK63" s="136"/>
-      <c r="AL63" s="136"/>
-      <c r="AM63" s="136"/>
-      <c r="AN63" s="136"/>
-    </row>
-    <row r="64" spans="4:40" x14ac:dyDescent="0.25">
-      <c r="D64" s="136" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B67" s="91" t="s">
-        <v>261</v>
-      </c>
-      <c r="D67" s="160" t="s">
-        <v>317</v>
-      </c>
-      <c r="E67" s="160"/>
-      <c r="F67" s="160"/>
-      <c r="G67" s="160"/>
-      <c r="H67" s="160"/>
-      <c r="I67" s="160"/>
-      <c r="J67" s="160"/>
-      <c r="K67" s="160"/>
-      <c r="L67" s="160"/>
-      <c r="M67" s="160"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="D68" s="160"/>
-      <c r="E68" s="160"/>
-      <c r="F68" s="160"/>
-      <c r="G68" s="160"/>
-      <c r="H68" s="160"/>
-      <c r="I68" s="160"/>
-      <c r="J68" s="160"/>
-      <c r="K68" s="160"/>
-      <c r="L68" s="160"/>
-      <c r="M68" s="160"/>
-    </row>
-    <row r="69" spans="2:29" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="160"/>
-      <c r="E69" s="160"/>
-      <c r="F69" s="160"/>
-      <c r="G69" s="160"/>
-      <c r="H69" s="160"/>
-      <c r="I69" s="160"/>
-      <c r="J69" s="160"/>
-      <c r="K69" s="160"/>
-      <c r="L69" s="160"/>
-      <c r="M69" s="160"/>
-    </row>
-    <row r="75" spans="2:29" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="B75" s="163" t="s">
-        <v>262</v>
-      </c>
-      <c r="C75" s="163"/>
-      <c r="D75" s="163"/>
-      <c r="E75" s="163"/>
-      <c r="F75" s="163"/>
-      <c r="G75" s="163"/>
-      <c r="H75" s="163"/>
-      <c r="I75" s="163"/>
-      <c r="J75" s="163"/>
-      <c r="K75" s="163"/>
-      <c r="L75" s="163"/>
-      <c r="M75" s="163"/>
-      <c r="N75" s="163"/>
-      <c r="O75" s="163"/>
-      <c r="P75" s="163"/>
-      <c r="Q75" s="163"/>
-      <c r="R75" s="163"/>
-      <c r="S75" s="163"/>
-      <c r="T75" s="163"/>
-      <c r="U75" s="163"/>
-      <c r="V75" s="163"/>
-      <c r="W75" s="163"/>
-      <c r="X75" s="163"/>
-      <c r="Y75" s="163"/>
-      <c r="Z75" s="163"/>
-      <c r="AA75" s="163"/>
-      <c r="AB75" s="137"/>
-      <c r="AC75" s="137"/>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B76" s="137"/>
-      <c r="C76" s="137"/>
-      <c r="D76" s="137"/>
-      <c r="E76" s="137"/>
-      <c r="F76" s="137"/>
-      <c r="G76" s="137"/>
-      <c r="H76" s="137"/>
-      <c r="I76" s="137"/>
-      <c r="J76" s="137"/>
-      <c r="K76" s="137"/>
-      <c r="L76" s="137"/>
-      <c r="M76" s="137"/>
-      <c r="N76" s="137"/>
-      <c r="O76" s="137"/>
-      <c r="P76" s="137"/>
-      <c r="Q76" s="137"/>
-      <c r="R76" s="137"/>
-      <c r="S76" s="137"/>
-      <c r="T76" s="137"/>
-      <c r="U76" s="137"/>
-      <c r="V76" s="137"/>
-      <c r="W76" s="137"/>
-      <c r="X76" s="137"/>
-      <c r="Y76" s="137"/>
-      <c r="Z76" s="137"/>
-      <c r="AA76" s="137"/>
-      <c r="AB76" s="137"/>
-      <c r="AC76" s="137"/>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B77" s="137" t="s">
-        <v>263</v>
-      </c>
-      <c r="C77" s="137"/>
-      <c r="D77" s="137"/>
-      <c r="E77" s="137"/>
-      <c r="F77" s="137"/>
-      <c r="G77" s="137"/>
-      <c r="H77" s="137"/>
-      <c r="I77" s="137"/>
-      <c r="J77" s="137"/>
-      <c r="K77" s="137"/>
-      <c r="L77" s="137"/>
-      <c r="M77" s="137"/>
-      <c r="N77" s="137"/>
-      <c r="O77" s="137"/>
-      <c r="P77" s="137"/>
-      <c r="Q77" s="137"/>
-      <c r="R77" s="137"/>
-      <c r="S77" s="137"/>
-      <c r="T77" s="137"/>
-      <c r="U77" s="137"/>
-      <c r="V77" s="137"/>
-      <c r="W77" s="137"/>
-      <c r="X77" s="137"/>
-      <c r="Y77" s="137"/>
-      <c r="Z77" s="137"/>
-      <c r="AA77" s="137"/>
-      <c r="AB77" s="137"/>
-      <c r="AC77" s="137"/>
-    </row>
-    <row r="78" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B78" s="137"/>
-      <c r="C78" s="137"/>
-      <c r="D78" s="137"/>
-      <c r="E78" s="137"/>
-      <c r="F78" s="137"/>
-      <c r="G78" s="137"/>
-      <c r="H78" s="137"/>
-      <c r="I78" s="137"/>
-      <c r="J78" s="137"/>
-      <c r="K78" s="137"/>
-      <c r="L78" s="137"/>
-      <c r="M78" s="137"/>
-      <c r="N78" s="137"/>
-      <c r="O78" s="137"/>
-      <c r="P78" s="137"/>
-      <c r="Q78" s="137"/>
-      <c r="R78" s="137"/>
-      <c r="S78" s="137"/>
-      <c r="T78" s="137"/>
-      <c r="U78" s="137"/>
-      <c r="V78" s="137"/>
-      <c r="W78" s="137"/>
-      <c r="X78" s="137"/>
-      <c r="Y78" s="137"/>
-      <c r="Z78" s="137"/>
-      <c r="AA78" s="137"/>
-      <c r="AB78" s="137"/>
-      <c r="AC78" s="137"/>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B79" s="162" t="s">
-        <v>264</v>
-      </c>
-      <c r="C79" s="162"/>
-      <c r="D79" s="162"/>
-      <c r="E79" s="162"/>
-      <c r="F79" s="162"/>
-      <c r="G79" s="162"/>
-      <c r="H79" s="162"/>
-      <c r="I79" s="162"/>
-      <c r="J79" s="162"/>
-      <c r="K79" s="162"/>
-      <c r="L79" s="162"/>
-      <c r="M79" s="162"/>
-      <c r="N79" s="162"/>
-      <c r="O79" s="162"/>
-      <c r="P79" s="162"/>
-      <c r="Q79" s="137"/>
-      <c r="R79" s="137"/>
-      <c r="S79" s="137"/>
-      <c r="T79" s="137"/>
-      <c r="U79" s="137"/>
-      <c r="V79" s="137"/>
-      <c r="W79" s="137"/>
-      <c r="X79" s="137"/>
-      <c r="Y79" s="137"/>
-      <c r="Z79" s="137"/>
-      <c r="AA79" s="137"/>
-      <c r="AB79" s="137"/>
-      <c r="AC79" s="137"/>
-    </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B80" s="162"/>
-      <c r="C80" s="162"/>
-      <c r="D80" s="162"/>
-      <c r="E80" s="162"/>
-      <c r="F80" s="162"/>
-      <c r="G80" s="162"/>
-      <c r="H80" s="162"/>
-      <c r="I80" s="162"/>
-      <c r="J80" s="162"/>
-      <c r="K80" s="162"/>
-      <c r="L80" s="162"/>
-      <c r="M80" s="162"/>
-      <c r="N80" s="162"/>
-      <c r="O80" s="162"/>
-      <c r="P80" s="162"/>
-      <c r="Q80" s="137"/>
-      <c r="R80" s="137"/>
-      <c r="S80" s="137"/>
-      <c r="T80" s="137"/>
-      <c r="U80" s="137"/>
-      <c r="V80" s="137"/>
-      <c r="W80" s="137"/>
-      <c r="X80" s="137"/>
-      <c r="Y80" s="137"/>
-      <c r="Z80" s="137"/>
-      <c r="AA80" s="137"/>
-      <c r="AB80" s="137"/>
-      <c r="AC80" s="137"/>
-    </row>
-    <row r="81" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B81" s="138" t="s">
-        <v>269</v>
-      </c>
-      <c r="C81" s="137"/>
-      <c r="D81" s="137"/>
-      <c r="E81" s="137"/>
-      <c r="F81" s="137"/>
-      <c r="G81" s="137"/>
-      <c r="H81" s="137"/>
-      <c r="I81" s="137"/>
-      <c r="J81" s="137"/>
-      <c r="K81" s="137"/>
-      <c r="L81" s="137"/>
-      <c r="M81" s="137"/>
-      <c r="N81" s="137"/>
-      <c r="O81" s="137"/>
-      <c r="P81" s="137"/>
-      <c r="Q81" s="137"/>
-      <c r="R81" s="137"/>
-      <c r="S81" s="137"/>
-      <c r="T81" s="137"/>
-      <c r="U81" s="137"/>
-      <c r="V81" s="137"/>
-      <c r="W81" s="137"/>
-      <c r="X81" s="137"/>
-      <c r="Y81" s="137"/>
-      <c r="Z81" s="137"/>
-      <c r="AA81" s="137"/>
-      <c r="AB81" s="137"/>
-      <c r="AC81" s="137"/>
-    </row>
-    <row r="82" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B82" s="162" t="s">
-        <v>265</v>
-      </c>
-      <c r="C82" s="162"/>
-      <c r="D82" s="162"/>
-      <c r="E82" s="162"/>
-      <c r="F82" s="162"/>
-      <c r="G82" s="162"/>
-      <c r="H82" s="162"/>
-      <c r="I82" s="162"/>
-      <c r="J82" s="162"/>
-      <c r="K82" s="162"/>
-      <c r="L82" s="162"/>
-      <c r="M82" s="162"/>
-      <c r="N82" s="162"/>
-      <c r="O82" s="162"/>
-      <c r="P82" s="162"/>
-      <c r="Q82" s="137"/>
-      <c r="R82" s="137"/>
-      <c r="S82" s="137"/>
-      <c r="T82" s="137"/>
-      <c r="U82" s="137"/>
-      <c r="V82" s="137"/>
-      <c r="W82" s="137"/>
-      <c r="X82" s="137"/>
-      <c r="Y82" s="137"/>
-      <c r="Z82" s="137"/>
-      <c r="AA82" s="137"/>
-      <c r="AB82" s="137"/>
-      <c r="AC82" s="137"/>
-    </row>
-    <row r="83" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B83" s="162"/>
-      <c r="C83" s="162"/>
-      <c r="D83" s="162"/>
-      <c r="E83" s="162"/>
-      <c r="F83" s="162"/>
-      <c r="G83" s="162"/>
-      <c r="H83" s="162"/>
-      <c r="I83" s="162"/>
-      <c r="J83" s="162"/>
-      <c r="K83" s="162"/>
-      <c r="L83" s="162"/>
-      <c r="M83" s="162"/>
-      <c r="N83" s="162"/>
-      <c r="O83" s="162"/>
-      <c r="P83" s="162"/>
-      <c r="Q83" s="137"/>
-      <c r="R83" s="137"/>
-      <c r="S83" s="137"/>
-      <c r="T83" s="137"/>
-      <c r="U83" s="137"/>
-      <c r="V83" s="137"/>
-      <c r="W83" s="137"/>
-      <c r="X83" s="137"/>
-      <c r="Y83" s="137"/>
-      <c r="Z83" s="137"/>
-      <c r="AA83" s="137"/>
-      <c r="AB83" s="137"/>
-      <c r="AC83" s="137"/>
-    </row>
-    <row r="84" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B84" s="138" t="s">
-        <v>266</v>
-      </c>
-      <c r="C84" s="137"/>
-      <c r="D84" s="137"/>
-      <c r="E84" s="137"/>
-      <c r="F84" s="137"/>
-      <c r="G84" s="137"/>
-      <c r="H84" s="137"/>
-      <c r="I84" s="137"/>
-      <c r="J84" s="137"/>
-      <c r="K84" s="137"/>
-      <c r="L84" s="137"/>
-      <c r="M84" s="137"/>
-      <c r="N84" s="137"/>
-      <c r="O84" s="137"/>
-      <c r="P84" s="137"/>
-      <c r="Q84" s="137"/>
-      <c r="R84" s="137"/>
-      <c r="S84" s="137"/>
-      <c r="T84" s="137"/>
-      <c r="U84" s="137"/>
-      <c r="V84" s="137"/>
-      <c r="W84" s="137"/>
-      <c r="X84" s="137"/>
-      <c r="Y84" s="137"/>
-      <c r="Z84" s="137"/>
-      <c r="AA84" s="137"/>
-      <c r="AB84" s="137"/>
-      <c r="AC84" s="137"/>
-    </row>
-    <row r="85" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B85" s="138" t="s">
-        <v>267</v>
-      </c>
-      <c r="C85" s="137"/>
-      <c r="D85" s="137"/>
-      <c r="E85" s="137"/>
-      <c r="F85" s="137"/>
-      <c r="G85" s="137"/>
-      <c r="H85" s="137"/>
-      <c r="I85" s="137"/>
-      <c r="J85" s="137"/>
-      <c r="K85" s="137"/>
-      <c r="L85" s="137"/>
-      <c r="M85" s="137"/>
-      <c r="N85" s="137"/>
-      <c r="O85" s="137"/>
-      <c r="P85" s="137"/>
-      <c r="Q85" s="137"/>
-      <c r="R85" s="137"/>
-      <c r="S85" s="137"/>
-      <c r="T85" s="137"/>
-      <c r="U85" s="137"/>
-      <c r="V85" s="137"/>
-      <c r="W85" s="137"/>
-      <c r="X85" s="137"/>
-      <c r="Y85" s="137"/>
-      <c r="Z85" s="137"/>
-      <c r="AA85" s="137"/>
-      <c r="AB85" s="137"/>
-      <c r="AC85" s="137"/>
-    </row>
-    <row r="86" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B86" s="137"/>
-      <c r="C86" s="137"/>
-      <c r="D86" s="137"/>
-      <c r="E86" s="137"/>
-      <c r="F86" s="137"/>
-      <c r="G86" s="137"/>
-      <c r="H86" s="137"/>
-      <c r="I86" s="137"/>
-      <c r="J86" s="137"/>
-      <c r="K86" s="137"/>
-      <c r="L86" s="137"/>
-      <c r="M86" s="137"/>
-      <c r="N86" s="137"/>
-      <c r="O86" s="137"/>
-      <c r="P86" s="137"/>
-      <c r="Q86" s="137"/>
-      <c r="R86" s="137"/>
-      <c r="S86" s="137"/>
-      <c r="T86" s="137"/>
-      <c r="U86" s="137"/>
-      <c r="V86" s="137"/>
-      <c r="W86" s="137"/>
-      <c r="X86" s="137"/>
-      <c r="Y86" s="137"/>
-      <c r="Z86" s="137"/>
-      <c r="AA86" s="137"/>
-      <c r="AB86" s="137"/>
-      <c r="AC86" s="137"/>
-    </row>
-    <row r="87" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B87" s="161" t="s">
-        <v>268</v>
-      </c>
-      <c r="C87" s="161"/>
-      <c r="D87" s="161"/>
-      <c r="E87" s="161"/>
-      <c r="F87" s="161"/>
-      <c r="G87" s="161"/>
-      <c r="H87" s="161"/>
-      <c r="I87" s="161"/>
-      <c r="J87" s="161"/>
-      <c r="K87" s="161"/>
-      <c r="L87" s="161"/>
-      <c r="M87" s="161"/>
-      <c r="N87" s="161"/>
-      <c r="O87" s="161"/>
-      <c r="P87" s="161"/>
-      <c r="Q87" s="137"/>
-      <c r="R87" s="137"/>
-      <c r="S87" s="137"/>
-      <c r="T87" s="137"/>
-      <c r="U87" s="137"/>
-      <c r="V87" s="137"/>
-      <c r="W87" s="137"/>
-      <c r="X87" s="137"/>
-      <c r="Y87" s="137"/>
-      <c r="Z87" s="137"/>
-      <c r="AA87" s="137"/>
-      <c r="AB87" s="137"/>
-      <c r="AC87" s="137"/>
-    </row>
-    <row r="88" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B88" s="161"/>
-      <c r="C88" s="161"/>
-      <c r="D88" s="161"/>
-      <c r="E88" s="161"/>
-      <c r="F88" s="161"/>
-      <c r="G88" s="161"/>
-      <c r="H88" s="161"/>
-      <c r="I88" s="161"/>
-      <c r="J88" s="161"/>
-      <c r="K88" s="161"/>
-      <c r="L88" s="161"/>
-      <c r="M88" s="161"/>
-      <c r="N88" s="161"/>
-      <c r="O88" s="161"/>
-      <c r="P88" s="161"/>
+      <c r="C81" s="136"/>
+      <c r="D81" s="136"/>
+      <c r="E81" s="136"/>
+      <c r="F81" s="136"/>
+      <c r="G81" s="136"/>
+      <c r="H81" s="136"/>
+      <c r="I81" s="136"/>
+      <c r="J81" s="136"/>
+      <c r="K81" s="136"/>
+      <c r="L81" s="136"/>
+      <c r="M81" s="136"/>
+      <c r="N81" s="136"/>
+      <c r="O81" s="136"/>
+      <c r="P81" s="136"/>
+      <c r="Q81" s="136"/>
+      <c r="R81" s="136"/>
+      <c r="S81" s="136"/>
+      <c r="T81" s="136"/>
+      <c r="U81" s="136"/>
+      <c r="V81" s="136"/>
+      <c r="W81" s="136"/>
+      <c r="X81" s="136"/>
+      <c r="Y81" s="136"/>
+      <c r="Z81" s="136"/>
+      <c r="AA81" s="136"/>
+      <c r="AB81" s="136"/>
+      <c r="AC81" s="136"/>
+    </row>
+    <row r="82" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B82" s="192" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" s="192"/>
+      <c r="D82" s="192"/>
+      <c r="E82" s="192"/>
+      <c r="F82" s="192"/>
+      <c r="G82" s="192"/>
+      <c r="H82" s="192"/>
+      <c r="I82" s="192"/>
+      <c r="J82" s="192"/>
+      <c r="K82" s="192"/>
+      <c r="L82" s="192"/>
+      <c r="M82" s="192"/>
+      <c r="N82" s="192"/>
+      <c r="O82" s="192"/>
+      <c r="P82" s="192"/>
+      <c r="Q82" s="136"/>
+      <c r="R82" s="136"/>
+      <c r="S82" s="136"/>
+      <c r="T82" s="136"/>
+      <c r="U82" s="136"/>
+      <c r="V82" s="136"/>
+      <c r="W82" s="136"/>
+      <c r="X82" s="136"/>
+      <c r="Y82" s="136"/>
+      <c r="Z82" s="136"/>
+      <c r="AA82" s="136"/>
+      <c r="AB82" s="136"/>
+      <c r="AC82" s="136"/>
+    </row>
+    <row r="83" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B83" s="192"/>
+      <c r="C83" s="192"/>
+      <c r="D83" s="192"/>
+      <c r="E83" s="192"/>
+      <c r="F83" s="192"/>
+      <c r="G83" s="192"/>
+      <c r="H83" s="192"/>
+      <c r="I83" s="192"/>
+      <c r="J83" s="192"/>
+      <c r="K83" s="192"/>
+      <c r="L83" s="192"/>
+      <c r="M83" s="192"/>
+      <c r="N83" s="192"/>
+      <c r="O83" s="192"/>
+      <c r="P83" s="192"/>
+      <c r="Q83" s="136"/>
+      <c r="R83" s="136"/>
+      <c r="S83" s="136"/>
+      <c r="T83" s="136"/>
+      <c r="U83" s="136"/>
+      <c r="V83" s="136"/>
+      <c r="W83" s="136"/>
+      <c r="X83" s="136"/>
+      <c r="Y83" s="136"/>
+      <c r="Z83" s="136"/>
+      <c r="AA83" s="136"/>
+      <c r="AB83" s="136"/>
+      <c r="AC83" s="136"/>
+    </row>
+    <row r="84" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B84" s="137" t="s">
+        <v>252</v>
+      </c>
+      <c r="C84" s="136"/>
+      <c r="D84" s="136"/>
+      <c r="E84" s="136"/>
+      <c r="F84" s="136"/>
+      <c r="G84" s="136"/>
+      <c r="H84" s="136"/>
+      <c r="I84" s="136"/>
+      <c r="J84" s="136"/>
+      <c r="K84" s="136"/>
+      <c r="L84" s="136"/>
+      <c r="M84" s="136"/>
+      <c r="N84" s="136"/>
+      <c r="O84" s="136"/>
+      <c r="P84" s="136"/>
+      <c r="Q84" s="136"/>
+      <c r="R84" s="136"/>
+      <c r="S84" s="136"/>
+      <c r="T84" s="136"/>
+      <c r="U84" s="136"/>
+      <c r="V84" s="136"/>
+      <c r="W84" s="136"/>
+      <c r="X84" s="136"/>
+      <c r="Y84" s="136"/>
+      <c r="Z84" s="136"/>
+      <c r="AA84" s="136"/>
+      <c r="AB84" s="136"/>
+      <c r="AC84" s="136"/>
+    </row>
+    <row r="85" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B85" s="137" t="s">
+        <v>253</v>
+      </c>
+      <c r="C85" s="136"/>
+      <c r="D85" s="136"/>
+      <c r="E85" s="136"/>
+      <c r="F85" s="136"/>
+      <c r="G85" s="136"/>
+      <c r="H85" s="136"/>
+      <c r="I85" s="136"/>
+      <c r="J85" s="136"/>
+      <c r="K85" s="136"/>
+      <c r="L85" s="136"/>
+      <c r="M85" s="136"/>
+      <c r="N85" s="136"/>
+      <c r="O85" s="136"/>
+      <c r="P85" s="136"/>
+      <c r="Q85" s="136"/>
+      <c r="R85" s="136"/>
+      <c r="S85" s="136"/>
+      <c r="T85" s="136"/>
+      <c r="U85" s="136"/>
+      <c r="V85" s="136"/>
+      <c r="W85" s="136"/>
+      <c r="X85" s="136"/>
+      <c r="Y85" s="136"/>
+      <c r="Z85" s="136"/>
+      <c r="AA85" s="136"/>
+      <c r="AB85" s="136"/>
+      <c r="AC85" s="136"/>
+    </row>
+    <row r="86" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B86" s="136"/>
+      <c r="C86" s="136"/>
+      <c r="D86" s="136"/>
+      <c r="E86" s="136"/>
+      <c r="F86" s="136"/>
+      <c r="G86" s="136"/>
+      <c r="H86" s="136"/>
+      <c r="I86" s="136"/>
+      <c r="J86" s="136"/>
+      <c r="K86" s="136"/>
+      <c r="L86" s="136"/>
+      <c r="M86" s="136"/>
+      <c r="N86" s="136"/>
+      <c r="O86" s="136"/>
+      <c r="P86" s="136"/>
+      <c r="Q86" s="136"/>
+      <c r="R86" s="136"/>
+      <c r="S86" s="136"/>
+      <c r="T86" s="136"/>
+      <c r="U86" s="136"/>
+      <c r="V86" s="136"/>
+      <c r="W86" s="136"/>
+      <c r="X86" s="136"/>
+      <c r="Y86" s="136"/>
+      <c r="Z86" s="136"/>
+      <c r="AA86" s="136"/>
+      <c r="AB86" s="136"/>
+      <c r="AC86" s="136"/>
+    </row>
+    <row r="87" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B87" s="191" t="s">
+        <v>254</v>
+      </c>
+      <c r="C87" s="191"/>
+      <c r="D87" s="191"/>
+      <c r="E87" s="191"/>
+      <c r="F87" s="191"/>
+      <c r="G87" s="191"/>
+      <c r="H87" s="191"/>
+      <c r="I87" s="191"/>
+      <c r="J87" s="191"/>
+      <c r="K87" s="191"/>
+      <c r="L87" s="191"/>
+      <c r="M87" s="191"/>
+      <c r="N87" s="191"/>
+      <c r="O87" s="191"/>
+      <c r="P87" s="191"/>
+      <c r="Q87" s="136"/>
+      <c r="R87" s="136"/>
+      <c r="S87" s="136"/>
+      <c r="T87" s="136"/>
+      <c r="U87" s="136"/>
+      <c r="V87" s="136"/>
+      <c r="W87" s="136"/>
+      <c r="X87" s="136"/>
+      <c r="Y87" s="136"/>
+      <c r="Z87" s="136"/>
+      <c r="AA87" s="136"/>
+      <c r="AB87" s="136"/>
+      <c r="AC87" s="136"/>
+    </row>
+    <row r="88" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B88" s="191"/>
+      <c r="C88" s="191"/>
+      <c r="D88" s="191"/>
+      <c r="E88" s="191"/>
+      <c r="F88" s="191"/>
+      <c r="G88" s="191"/>
+      <c r="H88" s="191"/>
+      <c r="I88" s="191"/>
+      <c r="J88" s="191"/>
+      <c r="K88" s="191"/>
+      <c r="L88" s="191"/>
+      <c r="M88" s="191"/>
+      <c r="N88" s="191"/>
+      <c r="O88" s="191"/>
+      <c r="P88" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6763,38 +6715,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A2:J24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="200" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-    </row>
-    <row r="4" spans="1:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="202" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="202"/>
-      <c r="H4" s="202"/>
-      <c r="I4" s="202"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="197" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="197"/>
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+    </row>
+    <row r="4" spans="1:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="199" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" s="199"/>
+      <c r="C4" s="199"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="199"/>
+      <c r="G4" s="199"/>
+      <c r="H4" s="199"/>
+      <c r="I4" s="199"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -6802,260 +6754,260 @@
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
     </row>
-    <row r="6" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="203" t="s">
+    <row r="6" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="200" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="200"/>
+      <c r="C6" s="200"/>
+      <c r="D6" s="200"/>
+      <c r="E6" s="200"/>
+      <c r="F6" s="200"/>
+      <c r="G6" s="200"/>
+      <c r="H6" s="200"/>
+      <c r="I6" s="200"/>
+    </row>
+    <row r="7" spans="1:10" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="201" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="201"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
+    </row>
+    <row r="8" spans="1:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="201" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="201"/>
+      <c r="C8" s="201"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
+      <c r="G8" s="201"/>
+      <c r="H8" s="201"/>
+      <c r="I8" s="201"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J10" s="64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="202" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="202"/>
+      <c r="C11" s="202"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="202"/>
+      <c r="F11" s="202"/>
+      <c r="G11" s="202"/>
+      <c r="H11" s="202"/>
+      <c r="I11" s="202"/>
+      <c r="J11" s="65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="203" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="203"/>
+      <c r="C12" s="203"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="203"/>
+      <c r="G12" s="203"/>
+      <c r="H12" s="203"/>
+      <c r="I12" s="203"/>
+      <c r="J12" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="203" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="203"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="203"/>
+      <c r="I13" s="203"/>
+      <c r="J13" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="203" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="203"/>
+      <c r="I14" s="203"/>
+      <c r="J14" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="203" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="203"/>
+      <c r="I15" s="203"/>
+      <c r="J15" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="198" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="198"/>
+      <c r="C16" s="198"/>
+      <c r="D16" s="198"/>
+      <c r="E16" s="198"/>
+      <c r="F16" s="198"/>
+      <c r="G16" s="198"/>
+      <c r="H16" s="198"/>
+      <c r="I16" s="198"/>
+      <c r="J16" s="65">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="198" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="198"/>
+      <c r="C17" s="198"/>
+      <c r="D17" s="198"/>
+      <c r="E17" s="198"/>
+      <c r="F17" s="198"/>
+      <c r="G17" s="198"/>
+      <c r="H17" s="198"/>
+      <c r="I17" s="198"/>
+      <c r="J17" s="65">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="203" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="203"/>
+      <c r="C18" s="203"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="203"/>
+      <c r="G18" s="203"/>
+      <c r="H18" s="203"/>
+      <c r="I18" s="203"/>
+      <c r="J18" s="65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="203" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="203"/>
+      <c r="C19" s="203"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="203"/>
+      <c r="G19" s="203"/>
+      <c r="H19" s="203"/>
+      <c r="I19" s="203"/>
+      <c r="J19" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="203" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="203"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="203"/>
+      <c r="G20" s="203"/>
+      <c r="H20" s="203"/>
+      <c r="I20" s="203"/>
+      <c r="J20" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="203" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="203"/>
-      <c r="C6" s="203"/>
-      <c r="D6" s="203"/>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="203"/>
-    </row>
-    <row r="7" spans="1:10" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="204" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="204"/>
-      <c r="C7" s="204"/>
-      <c r="D7" s="204"/>
-      <c r="E7" s="204"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="204"/>
-      <c r="H7" s="204"/>
-      <c r="I7" s="204"/>
-    </row>
-    <row r="8" spans="1:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="204" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="204"/>
-      <c r="C8" s="204"/>
-      <c r="D8" s="204"/>
-      <c r="E8" s="204"/>
-      <c r="F8" s="204"/>
-      <c r="G8" s="204"/>
-      <c r="H8" s="204"/>
-      <c r="I8" s="204"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J10" s="65" t="s">
+      <c r="B21" s="203"/>
+      <c r="C21" s="203"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="203"/>
+      <c r="H21" s="203"/>
+      <c r="I21" s="203"/>
+      <c r="J21" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="203" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="203"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203"/>
+      <c r="G22" s="203"/>
+      <c r="H22" s="203"/>
+      <c r="I22" s="203"/>
+      <c r="J22" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="198" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="205" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="205"/>
-      <c r="C11" s="205"/>
-      <c r="D11" s="205"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="205"/>
-      <c r="G11" s="205"/>
-      <c r="H11" s="205"/>
-      <c r="I11" s="205"/>
-      <c r="J11" s="66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="206" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="206"/>
-      <c r="C12" s="206"/>
-      <c r="D12" s="206"/>
-      <c r="E12" s="206"/>
-      <c r="F12" s="206"/>
-      <c r="G12" s="206"/>
-      <c r="H12" s="206"/>
-      <c r="I12" s="206"/>
-      <c r="J12" s="66">
+      <c r="B23" s="198"/>
+      <c r="C23" s="198"/>
+      <c r="D23" s="198"/>
+      <c r="E23" s="198"/>
+      <c r="F23" s="198"/>
+      <c r="G23" s="198"/>
+      <c r="H23" s="198"/>
+      <c r="I23" s="198"/>
+      <c r="J23" s="65">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="206"/>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-      <c r="F13" s="206"/>
-      <c r="G13" s="206"/>
-      <c r="H13" s="206"/>
-      <c r="I13" s="206"/>
-      <c r="J13" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-      <c r="F14" s="206"/>
-      <c r="G14" s="206"/>
-      <c r="H14" s="206"/>
-      <c r="I14" s="206"/>
-      <c r="J14" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="206" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="206"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-      <c r="F15" s="206"/>
-      <c r="G15" s="206"/>
-      <c r="H15" s="206"/>
-      <c r="I15" s="206"/>
-      <c r="J15" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="201" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
-      <c r="F16" s="201"/>
-      <c r="G16" s="201"/>
-      <c r="H16" s="201"/>
-      <c r="I16" s="201"/>
-      <c r="J16" s="66">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="201" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="201"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="201"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="201"/>
-      <c r="J17" s="66">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="206" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="206"/>
-      <c r="C18" s="206"/>
-      <c r="D18" s="206"/>
-      <c r="E18" s="206"/>
-      <c r="F18" s="206"/>
-      <c r="G18" s="206"/>
-      <c r="H18" s="206"/>
-      <c r="I18" s="206"/>
-      <c r="J18" s="66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="206" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="206"/>
-      <c r="C19" s="206"/>
-      <c r="D19" s="206"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="206"/>
-      <c r="G19" s="206"/>
-      <c r="H19" s="206"/>
-      <c r="I19" s="206"/>
-      <c r="J19" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="206" t="s">
-        <v>96</v>
-      </c>
-      <c r="B20" s="206"/>
-      <c r="C20" s="206"/>
-      <c r="D20" s="206"/>
-      <c r="E20" s="206"/>
-      <c r="F20" s="206"/>
-      <c r="G20" s="206"/>
-      <c r="H20" s="206"/>
-      <c r="I20" s="206"/>
-      <c r="J20" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="206" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="206"/>
-      <c r="C21" s="206"/>
-      <c r="D21" s="206"/>
-      <c r="E21" s="206"/>
-      <c r="F21" s="206"/>
-      <c r="G21" s="206"/>
-      <c r="H21" s="206"/>
-      <c r="I21" s="206"/>
-      <c r="J21" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="206" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="206"/>
-      <c r="C22" s="206"/>
-      <c r="D22" s="206"/>
-      <c r="E22" s="206"/>
-      <c r="F22" s="206"/>
-      <c r="G22" s="206"/>
-      <c r="H22" s="206"/>
-      <c r="I22" s="206"/>
-      <c r="J22" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="201" t="s">
-        <v>99</v>
-      </c>
-      <c r="B23" s="201"/>
-      <c r="C23" s="201"/>
-      <c r="D23" s="201"/>
-      <c r="E23" s="201"/>
-      <c r="F23" s="201"/>
-      <c r="G23" s="201"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="64"/>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7091,164 +7043,164 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07216399-A1CF-4A16-9C8D-1B78A6776C33}">
   <dimension ref="B1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="26.109375" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" customWidth="1"/>
+    <col min="6" max="6" width="26.140625" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B1" s="207" t="s">
-        <v>216</v>
-      </c>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-    </row>
-    <row r="3" spans="2:7" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="B3" s="113" t="s">
+    <row r="1" spans="2:7" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B1" s="204" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+    </row>
+    <row r="3" spans="2:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B3" s="112" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="112" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="112" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="113" t="s">
+      <c r="F3" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="G3" s="112" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B4" s="113" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="114" t="s">
+        <v>174</v>
+      </c>
+      <c r="E4" s="114" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="114" t="s">
+        <v>176</v>
+      </c>
+      <c r="G4" s="114" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B5" s="115" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="116" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="116" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="116" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="D3" s="113" t="s">
+      <c r="G5" s="116" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B6" s="117" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="E3" s="113" t="s">
+      <c r="D6" s="118" t="s">
         <v>184</v>
       </c>
-      <c r="F3" s="113" t="s">
+      <c r="E6" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="G3" s="113" t="s">
+      <c r="F6" s="118" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="B4" s="114" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="115" t="s">
+      <c r="G6" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="115" t="s">
+    </row>
+    <row r="7" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B7" s="119" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="120" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="115" t="s">
+      <c r="D7" s="120" t="s">
         <v>189</v>
       </c>
-      <c r="F4" s="115" t="s">
+      <c r="E7" s="120" t="s">
         <v>190</v>
       </c>
-      <c r="G4" s="115" t="s">
+      <c r="F7" s="120" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
+      <c r="G7" s="120" t="s">
         <v>192</v>
       </c>
-      <c r="C5" s="117" t="s">
+    </row>
+    <row r="8" spans="2:7" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="121" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="117" t="s">
+      <c r="C8" s="122" t="s">
         <v>194</v>
       </c>
-      <c r="E5" s="117" t="s">
+      <c r="D8" s="122" t="s">
         <v>195</v>
       </c>
-      <c r="F5" s="117" t="s">
+      <c r="E8" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="G5" s="117" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="B6" s="118" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="119" t="s">
+      <c r="F8" s="122" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="G8" s="122" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="123" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="124" t="s">
         <v>198</v>
       </c>
-      <c r="E6" s="119" t="s">
+      <c r="D9" s="124" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="119" t="s">
+      <c r="E9" s="124" t="s">
         <v>200</v>
       </c>
-      <c r="G6" s="119" t="s">
+      <c r="F9" s="124" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="B7" s="120" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="121" t="s">
-        <v>202</v>
-      </c>
-      <c r="D7" s="121" t="s">
-        <v>203</v>
-      </c>
-      <c r="E7" s="121" t="s">
-        <v>204</v>
-      </c>
-      <c r="F7" s="121" t="s">
-        <v>205</v>
-      </c>
-      <c r="G7" s="121" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="B8" s="122" t="s">
-        <v>207</v>
-      </c>
-      <c r="C8" s="123" t="s">
-        <v>208</v>
-      </c>
-      <c r="D8" s="123" t="s">
-        <v>209</v>
-      </c>
-      <c r="E8" s="123" t="s">
-        <v>210</v>
-      </c>
-      <c r="F8" s="123" t="s">
-        <v>211</v>
-      </c>
-      <c r="G8" s="123" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="66" x14ac:dyDescent="0.25">
-      <c r="B9" s="124" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="125" t="s">
-        <v>212</v>
-      </c>
-      <c r="D9" s="125" t="s">
-        <v>213</v>
-      </c>
-      <c r="E9" s="125" t="s">
-        <v>214</v>
-      </c>
-      <c r="F9" s="125" t="s">
-        <v>215</v>
-      </c>
-      <c r="G9" s="125" t="s">
-        <v>156</v>
+      <c r="G9" s="124" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
